--- a/output/independent-code-review/claude/sample-1/workpaper.xlsx
+++ b/output/independent-code-review/claude/sample-1/workpaper.xlsx
@@ -23,7 +23,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.0000"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -52,7 +52,7 @@
     <font>
       <name val="SF Pro Text"/>
       <b val="1"/>
-      <color rgb="00A17321"/>
+      <color rgb="00148F72"/>
       <sz val="16"/>
     </font>
     <font>
@@ -75,12 +75,6 @@
     <font>
       <name val="SF Pro Text"/>
       <b val="1"/>
-      <color rgb="00A17321"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="SF Pro Text"/>
-      <b val="1"/>
       <color rgb="00148F72"/>
       <sz val="10"/>
     </font>
@@ -96,17 +90,11 @@
       <sz val="10"/>
     </font>
     <font>
-      <name val="SF Pro Text"/>
-      <b val="1"/>
-      <color rgb="00A17321"/>
-      <sz val="10"/>
-    </font>
-    <font>
       <b val="1"/>
       <color rgb="000B362C"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -115,17 +103,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F5EDD9"/>
+        <fgColor rgb="00E7F3EE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FAF8F3"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E7F3EE"/>
       </patternFill>
     </fill>
   </fills>
@@ -199,7 +182,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -213,27 +196,23 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -630,7 +609,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>CONTROL INCONCLUSIVE</t>
+          <t>CONTROL PASS</t>
         </is>
       </c>
     </row>
@@ -666,7 +645,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>03 Jul 2026, 03:13 UTC</t>
+          <t>03 Jul 2026, 03:35 UTC</t>
         </is>
       </c>
     </row>
@@ -680,7 +659,7 @@
     <row r="11" ht="60" customHeight="1">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>The control cannot be signed off from this evidence bundle. 1 attribute(s) need further evidence, 2 passed, and none positively failed. Request the missing evidence and re-audit.</t>
+          <t>The control passed. All 3 attribute(s) tested cleanly with citation-backed evidence. No follow-up findings raised.</t>
         </is>
       </c>
     </row>
@@ -692,14 +671,14 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="inlineStr">
-        <is>
-          <t>WARN</t>
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>Insufficient evidence: Testing is performed in accordance with the testing policy</t>
+          <t>Code Reviews are performed prior to committing a change to the main branch</t>
         </is>
       </c>
     </row>
@@ -711,7 +690,7 @@
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>Code Reviews are performed prior to committing a change to the main branch</t>
+          <t>Code Review approvals are performed by independent code reviewers</t>
         </is>
       </c>
     </row>
@@ -723,7 +702,7 @@
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>Code Review approvals are performed by independent code reviewers</t>
+          <t>Testing is performed in accordance with the testing policy</t>
         </is>
       </c>
     </row>
@@ -735,14 +714,14 @@
       </c>
     </row>
     <row r="19" ht="30" customHeight="1">
-      <c r="A19" s="10" t="inlineStr">
+      <c r="A19" s="9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>Provide additional evidence to close “Testing is performed in accordance with the testing policy”. Specifically: The CI run for PR #62754 completed successfully with 15 matrix test jobs green plus coverage, lint, typecheck, smoke, browser-integration and baselines jobs all passing (36 of 37 checks passed on the PR), which supports test execution in CI and PR status visibility.</t>
+          <t>No open actions from this run — retain evidence + workpaper for the audit file.</t>
         </is>
       </c>
     </row>
@@ -754,54 +733,54 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="11" t="inlineStr">
+      <c r="A22" s="10" t="inlineStr">
         <is>
           <t>Decision (Accept / Rework / Reject)</t>
         </is>
       </c>
-      <c r="B22" s="12" t="inlineStr"/>
-      <c r="C22" s="13" t="n"/>
-      <c r="D22" s="14" t="n"/>
+      <c r="B22" s="11" t="inlineStr"/>
+      <c r="C22" s="12" t="n"/>
+      <c r="D22" s="13" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="11" t="inlineStr">
+      <c r="A23" s="10" t="inlineStr">
         <is>
           <t>Reviewer name</t>
         </is>
       </c>
-      <c r="B23" s="12" t="inlineStr"/>
-      <c r="C23" s="13" t="n"/>
-      <c r="D23" s="14" t="n"/>
+      <c r="B23" s="11" t="inlineStr"/>
+      <c r="C23" s="12" t="n"/>
+      <c r="D23" s="13" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="11" t="inlineStr">
+      <c r="A24" s="10" t="inlineStr">
         <is>
           <t>Reviewer role</t>
         </is>
       </c>
-      <c r="B24" s="12" t="inlineStr"/>
-      <c r="C24" s="13" t="n"/>
-      <c r="D24" s="14" t="n"/>
+      <c r="B24" s="11" t="inlineStr"/>
+      <c r="C24" s="12" t="n"/>
+      <c r="D24" s="13" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="11" t="inlineStr">
+      <c r="A25" s="10" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B25" s="12" t="inlineStr"/>
-      <c r="C25" s="13" t="n"/>
-      <c r="D25" s="14" t="n"/>
+      <c r="B25" s="11" t="inlineStr"/>
+      <c r="C25" s="12" t="n"/>
+      <c r="D25" s="13" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="11" t="inlineStr">
+      <c r="A26" s="10" t="inlineStr">
         <is>
           <t>Comments</t>
         </is>
       </c>
-      <c r="B26" s="12" t="inlineStr"/>
-      <c r="C26" s="13" t="n"/>
-      <c r="D26" s="14" t="n"/>
+      <c r="B26" s="11" t="inlineStr"/>
+      <c r="C26" s="12" t="n"/>
+      <c r="D26" s="13" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="13">
@@ -841,120 +820,119 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="15" t="inlineStr">
+      <c r="A1" s="14" t="inlineStr">
         <is>
           <t>Attribute</t>
         </is>
       </c>
-      <c r="B1" s="15" t="inlineStr">
+      <c r="B1" s="14" t="inlineStr">
         <is>
           <t>Verdict</t>
         </is>
       </c>
-      <c r="C1" s="15" t="inlineStr">
+      <c r="C1" s="14" t="inlineStr">
         <is>
           <t>Confidence</t>
         </is>
       </c>
-      <c r="D1" s="15" t="inlineStr">
+      <c r="D1" s="14" t="inlineStr">
         <is>
           <t>Rationale</t>
         </is>
       </c>
-      <c r="E1" s="15" t="inlineStr">
+      <c r="E1" s="14" t="inlineStr">
         <is>
           <t>Citations</t>
         </is>
       </c>
-      <c r="F1" s="15" t="inlineStr">
+      <c r="F1" s="14" t="inlineStr">
         <is>
           <t>Exceptions considered</t>
         </is>
       </c>
     </row>
     <row r="2" ht="80" customHeight="1">
-      <c r="A2" s="16" t="inlineStr">
+      <c r="A2" s="15" t="inlineStr">
         <is>
           <t>Code Reviews are performed prior to committing a change to the main branch</t>
         </is>
       </c>
-      <c r="B2" s="17" t="inlineStr">
+      <c r="B2" s="16" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="C2" s="16" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="D2" s="16" t="inlineStr">
-        <is>
-          <t>A pull request (#62754) exists for the change, providing the required code review record. The PR page shows RyanCavanaugh approved (green checkmark) at 17 hours ago, and the merge into microsoft:main occurred 16 hours ago — review precedes merge. The change went through a PR rather than being committed directly to main. Note: reviewer independence from author jakebailey is a separate attribute; this attribute only concerns whether a review occurred prior to merge, which it did.</t>
-        </is>
-      </c>
-      <c r="E2" s="16" t="n">
-        <v>3</v>
-      </c>
-      <c r="F2" s="16" t="inlineStr">
-        <is>
-          <t>Copilot AI reviewer presence — noted but not relevant to this attribute; independence/human-reviewer question belongs to a separate attribute.
-31 commits vs 1 merged commit ambiguity — could implicate the 'no additional commits after approval' criterion, but relative timestamps show approval and merge both occurred within the same window and PR was auto-merge enabled; no evidence of post-approval unreviewed commits.</t>
+      <c r="C2" s="15" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="D2" s="15" t="inlineStr">
+        <is>
+          <t>A pull request record (PR #62754) exists for the change, and RyanCavanaugh approved the PR 17 hours ago while the merge into microsoft:main occurred 16 hours ago — approval precedes merge. The PR shows a 'Merged' badge and the footer confirms the branch was merged via PR (not a direct push to main). This attribute concerns existence and timing of review vs merge; reviewer independence is a separate attribute.</t>
+        </is>
+      </c>
+      <c r="E2" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="F2" s="15" t="inlineStr">
+        <is>
+          <t>Reviewer independence (Copilot AI reviewer is not an independent human) is not in scope for this attribute — this attribute tests timing/existence of a code review before merge, which is satisfied by RyanCavanaugh's human approval prior to merge.</t>
         </is>
       </c>
     </row>
     <row r="3" ht="80" customHeight="1">
-      <c r="A3" s="16" t="inlineStr">
+      <c r="A3" s="15" t="inlineStr">
         <is>
           <t>Code Review approvals are performed by independent code reviewers</t>
         </is>
       </c>
-      <c r="B3" s="17" t="inlineStr">
+      <c r="B3" s="16" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="C3" s="16" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="D3" s="16" t="inlineStr">
-        <is>
-          <t>PR #62754 was authored and committed by jakebailey and approved by RyanCavanaugh — a different named human — satisfying the 4-eyes principle. RyanCavanaugh's approval carries a green checkmark; Copilot's AI review is disregarded as not an independent human reviewer. The PR was merged into microsoft:main, indicating the approver had authority to approve for the repository. No evidence suggests RyanCavanaugh committed or co-authored the change (all 31 commits attributed to jakebailey).</t>
-        </is>
-      </c>
-      <c r="E3" s="16" t="n">
-        <v>3</v>
-      </c>
-      <c r="F3" s="16" t="inlineStr">
-        <is>
-          <t>Considered whether Copilot's AI review could count toward independent review — rejected, as Copilot is an AI bot (AI badge visible) and does not represent an independent human reviewer. This does not affect the verdict because a separate independent human approval by RyanCavanaugh is present.</t>
+      <c r="C3" s="15" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="D3" s="15" t="inlineStr">
+        <is>
+          <t>The PR #62754 was authored and merged by jakebailey, and shows an approving review from RyanCavanaugh (a different named human), documented in the GitHub Reviewers sidebar with a green check. Copilot's review is explicitly not counted as an independent human review, but RyanCavanaugh's approval satisfies the 4-eyes requirement. There is no indication RyanCavanaugh committed or co-authored the change (author/committer/assignee are all jakebailey), and the merge was not a self-approval since a separate approver granted the required review.</t>
+        </is>
+      </c>
+      <c r="E3" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="F3" s="15" t="inlineStr">
+        <is>
+          <t>Copilot as reviewer — rejected as an independent human reviewer per guidance; however RyanCavanaugh provides the required independent human approval so the criterion is still met.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="80" customHeight="1">
-      <c r="A4" s="16" t="inlineStr">
+      <c r="A4" s="15" t="inlineStr">
         <is>
           <t>Testing is performed in accordance with the testing policy</t>
         </is>
       </c>
-      <c r="B4" s="18" t="inlineStr">
-        <is>
-          <t>FURTHER_EVIDENCE_REQUIRED</t>
-        </is>
-      </c>
-      <c r="C4" s="16" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="D4" s="16" t="inlineStr">
-        <is>
-          <t>The CI run for PR #62754 completed successfully with 15 matrix test jobs green plus coverage, lint, typecheck, smoke, browser-integration and baselines jobs all passing (36 of 37 checks passed on the PR), which supports test execution in CI and PR status visibility. However, the provided coverage report screenshot cannot be tied to this PR/commit (no repo, commit SHA, branch, or timestamp visible), and the aggregate report shows a file (src/compiler/debug.ts) below thresholds — but without knowing whether the PR modified that file we cannot judge new-code coverage. Also no evidence shows security scan results were reviewed/approved or that manual smoke tests were completed. To flip to SUCCESS: provide a coverage report tied to commit ea48ded showing ≥80% line, ≥70% branch, ≥80% function coverage for the changed files, plus evidence that security scans and (if applicable) smoke tests were reviewed. Note: the PR is a small test-size shrink (+10/-10 across 4 files) which may qualify as a behavior-preserving refactor exception, but no such exception basis is documented in the evidence provided.</t>
-        </is>
-      </c>
-      <c r="E4" s="16" t="n">
+      <c r="B4" s="16" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="C4" s="15" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="D4" s="15" t="inlineStr">
+        <is>
+          <t>The change is a test-only reduction (shrinks the Digits type in a compiler relationComplexityError test from 10 to 8 literals), affecting only test files under tests/cases and tests/baselines — a behavior-preserving test refactor rather than production logic. The CI pipeline ran successfully (Success, 17m 44s, 36 of 37 checks passed) including coverage, lint, typecheck, smoke, baselines, and multi-OS/multi-Node matrix jobs, with a coverage artifact produced. The coverage report shows repository-wide metrics well above policy thresholds: Statements 94.62%, Branches 89.48% (≥70%), Functions 94.79% (≥80%). Test results are visible in PR status checks and were executed pre-merge. No security/payment/auth flows are touched. Criteria are met on the evidence available.</t>
+        </is>
+      </c>
+      <c r="E4" s="15" t="n">
         <v>5</v>
       </c>
-      <c r="F4" s="16" t="inlineStr">
-        <is>
-          <t>Behavior-preserving refactor exception considered: the PR title ('Shrink relationComplexityError test size') and small diff (+10/-10 across 4 files) suggest a test-only/refactor change that could qualify, but no exception basis is explicitly documented on the PR in the evidence provided, so the exception cannot be affirmatively accepted.
-Build/deployment scripts exception considered and rejected: change appears to touch test code, not CI/build scripts.</t>
+      <c r="F4" s="15" t="inlineStr">
+        <is>
+          <t>Refactoring with No Behavioral Changes: Accepted as applicable — the PR modifies only test source and baseline reference files to reduce test complexity/runtime ('Getting tired of this test timing out on slower builders'), with no production code changes. Existing test coverage in CI verifies behavior.
+Coverage report not tied by commit SHA/PR to this specific change on the report page — noted as an ambiguity, but the CI run for commit 9e76dd2 produced a coverage artifact and the repository-wide coverage metrics all exceed thresholds, so this does not overturn SUCCESS.</t>
         </is>
       </c>
     </row>
@@ -969,7 +947,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -979,266 +957,310 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="15" t="inlineStr">
+      <c r="A1" s="14" t="inlineStr">
         <is>
           <t>Attribute</t>
         </is>
       </c>
-      <c r="B1" s="15" t="inlineStr">
+      <c r="B1" s="14" t="inlineStr">
         <is>
           <t>File</t>
         </is>
       </c>
-      <c r="C1" s="15" t="inlineStr">
+      <c r="C1" s="14" t="inlineStr">
         <is>
           <t>Locator</t>
         </is>
       </c>
-      <c r="D1" s="15" t="inlineStr">
+      <c r="D1" s="14" t="inlineStr">
         <is>
           <t>Observation</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="16" t="inlineStr">
+      <c r="A2" s="15" t="inlineStr">
         <is>
           <t>Code Reviews are performed prior to committing a change to the main branch</t>
         </is>
       </c>
-      <c r="B2" s="16" t="inlineStr">
+      <c r="B2" s="15" t="inlineStr">
         <is>
           <t>Screenshot 2025-11-14 at 14-28-31 Shrink relationComplexityError test size by jakebailey · Pull Request #62754 · microsoft_TypeScript.png</t>
         </is>
       </c>
-      <c r="C2" s="16" t="inlineStr">
-        <is>
-          <t>PR header and timeline</t>
-        </is>
-      </c>
-      <c r="D2" s="16" t="inlineStr">
-        <is>
-          <t>PR #62754 exists; opened/review requested 17 hours ago; merge commit ea48ded into microsoft:main 16 hours ago.</t>
+      <c r="C2" s="15" t="inlineStr">
+        <is>
+          <t>PR header / Merged badge</t>
+        </is>
+      </c>
+      <c r="D2" s="15" t="inlineStr">
+        <is>
+          <t>Purple 'Merged' badge and header 'jakebailey merged 1 commit into microsoft:main from jakebailey:relationComplexityErrorSmaller 16 hours ago' — confirms PR record exists and was merged to main.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="16" t="inlineStr">
+      <c r="A3" s="15" t="inlineStr">
         <is>
           <t>Code Reviews are performed prior to committing a change to the main branch</t>
         </is>
       </c>
-      <c r="B3" s="16" t="inlineStr">
+      <c r="B3" s="15" t="inlineStr">
         <is>
           <t>Screenshot 2025-11-14 at 14-28-31 Shrink relationComplexityError test size by jakebailey · Pull Request #62754 · microsoft_TypeScript.png</t>
         </is>
       </c>
-      <c r="C3" s="16" t="inlineStr">
-        <is>
-          <t>Reviewers panel</t>
-        </is>
-      </c>
-      <c r="D3" s="16" t="inlineStr">
-        <is>
-          <t>RyanCavanaugh shows a green checkmark approval on the PR prior to the merge event.</t>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>Timeline event (approval)</t>
+        </is>
+      </c>
+      <c r="D3" s="15" t="inlineStr">
+        <is>
+          <t>'RyanCavanaugh approved these changes 17 hours ago' — approval timestamp precedes the merge timestamp (16 hours ago).</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="16" t="inlineStr">
+      <c r="A4" s="15" t="inlineStr">
         <is>
           <t>Code Reviews are performed prior to committing a change to the main branch</t>
         </is>
       </c>
-      <c r="B4" s="16" t="inlineStr">
+      <c r="B4" s="15" t="inlineStr">
         <is>
           <t>Screenshot 2025-11-14 at 14-28-31 Shrink relationComplexityError test size by jakebailey · Pull Request #62754 · microsoft_TypeScript.png</t>
         </is>
       </c>
-      <c r="C4" s="16" t="inlineStr">
-        <is>
-          <t>Merge status header</t>
-        </is>
-      </c>
-      <c r="D4" s="16" t="inlineStr">
-        <is>
-          <t>PR was merged into microsoft:main via merge commit (ea48ded), not a direct push to main.</t>
+      <c r="C4" s="15" t="inlineStr">
+        <is>
+          <t>Merge timeline event</t>
+        </is>
+      </c>
+      <c r="D4" s="15" t="inlineStr">
+        <is>
+          <t>'jakebailey merged commit ea48ded into microsoft:main 16 hours ago' — merge into main occurred after the approval one hour earlier.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="16" t="inlineStr">
+      <c r="A5" s="15" t="inlineStr">
+        <is>
+          <t>Code Reviews are performed prior to committing a change to the main branch</t>
+        </is>
+      </c>
+      <c r="B5" s="15" t="inlineStr">
+        <is>
+          <t>Screenshot 2025-11-14 at 14-28-31 Shrink relationComplexityError test size by jakebailey · Pull Request #62754 · microsoft_TypeScript.png</t>
+        </is>
+      </c>
+      <c r="C5" s="15" t="inlineStr">
+        <is>
+          <t>Footer banner</t>
+        </is>
+      </c>
+      <c r="D5" s="15" t="inlineStr">
+        <is>
+          <t>'Pull request successfully merged and closed — the branch has been merged.' confirms change reached main via reviewed PR, not direct commit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="15" t="inlineStr">
         <is>
           <t>Code Review approvals are performed by independent code reviewers</t>
         </is>
       </c>
-      <c r="B5" s="16" t="inlineStr">
+      <c r="B6" s="15" t="inlineStr">
         <is>
           <t>Screenshot 2025-11-14 at 14-28-31 Shrink relationComplexityError test size by jakebailey · Pull Request #62754 · microsoft_TypeScript.png</t>
         </is>
       </c>
-      <c r="C5" s="16" t="inlineStr">
-        <is>
-          <t>PR header and Reviewers panel</t>
-        </is>
-      </c>
-      <c r="D5" s="16" t="inlineStr">
-        <is>
-          <t>Author/committer is jakebailey; RyanCavanaugh appears as reviewer with an approval checkmark. Copilot appears as an AI reviewer (AI badge, no approval checkmark).</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="16" t="inlineStr">
+      <c r="C6" s="15" t="inlineStr">
+        <is>
+          <t>Timeline event, mid-page</t>
+        </is>
+      </c>
+      <c r="D6" s="15" t="inlineStr">
+        <is>
+          <t>'RyanCavanaugh approved these changes 17 hours ago' with green check and 'View reviewed changes' link.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="15" t="inlineStr">
         <is>
           <t>Code Review approvals are performed by independent code reviewers</t>
         </is>
       </c>
-      <c r="B6" s="16" t="inlineStr">
+      <c r="B7" s="15" t="inlineStr">
         <is>
           <t>Screenshot 2025-11-14 at 14-28-31 Shrink relationComplexityError test size by jakebailey · Pull Request #62754 · microsoft_TypeScript.png</t>
         </is>
       </c>
-      <c r="C6" s="16" t="inlineStr">
-        <is>
-          <t>Merge status banner</t>
-        </is>
-      </c>
-      <c r="D6" s="16" t="inlineStr">
-        <is>
-          <t>PR merged into microsoft:main 16 hours ago as commit ea48ded, indicating approver had merge/approval authority.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="16" t="inlineStr">
+      <c r="C7" s="15" t="inlineStr">
+        <is>
+          <t>PR header</t>
+        </is>
+      </c>
+      <c r="D7" s="15" t="inlineStr">
+        <is>
+          <t>'jakebailey merged 1 commit into microsoft:main from jakebailey:relationComplexityErrorSmaller' — identifies jakebailey as author and merger.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="15" t="inlineStr">
         <is>
           <t>Code Review approvals are performed by independent code reviewers</t>
         </is>
       </c>
-      <c r="B7" s="16" t="inlineStr">
+      <c r="B8" s="15" t="inlineStr">
+        <is>
+          <t>Screenshot 2025-11-14 at 14-28-31 Shrink relationComplexityError test size by jakebailey · Pull Request #62754 · microsoft_TypeScript.png</t>
+        </is>
+      </c>
+      <c r="C8" s="15" t="inlineStr">
+        <is>
+          <t>Right sidebar — Reviewers panel</t>
+        </is>
+      </c>
+      <c r="D8" s="15" t="inlineStr">
+        <is>
+          <t>Reviewers listed: Copilot and RyanCavanaugh, with green check next to RyanCavanaugh indicating approval; Assignees: jakebailey.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="15" t="inlineStr">
+        <is>
+          <t>Code Review approvals are performed by independent code reviewers</t>
+        </is>
+      </c>
+      <c r="B9" s="15" t="inlineStr">
+        <is>
+          <t>Screenshot 2025-11-14 at 14-28-31 Shrink relationComplexityError test size by jakebailey · Pull Request #62754 · microsoft_TypeScript.png</t>
+        </is>
+      </c>
+      <c r="C9" s="15" t="inlineStr">
+        <is>
+          <t>Merge status banner near bottom</t>
+        </is>
+      </c>
+      <c r="D9" s="15" t="inlineStr">
+        <is>
+          <t>'jakebailey merged commit ea48ded into microsoft:main 16 hours ago' — confirms merge occurred after RyanCavanaugh's approval was recorded.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="15" t="inlineStr">
+        <is>
+          <t>Testing is performed in accordance with the testing policy</t>
+        </is>
+      </c>
+      <c r="B10" s="15" t="inlineStr">
+        <is>
+          <t>Screenshot 2025-11-14 at 14-27-50 Coverage Report.png</t>
+        </is>
+      </c>
+      <c r="C10" s="15" t="inlineStr">
+        <is>
+          <t>Summary row (top of coverage table)</t>
+        </is>
+      </c>
+      <c r="D10" s="15" t="inlineStr">
+        <is>
+          <t>Statements 94.62%, Branches 89.48%, Functions 94.79%, Bytes 95.96% — all above policy thresholds (statements ≥80, branches ≥70, functions ≥80).</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="15" t="inlineStr">
+        <is>
+          <t>Testing is performed in accordance with the testing policy</t>
+        </is>
+      </c>
+      <c r="B11" s="15" t="inlineStr">
+        <is>
+          <t>Screenshot 2025-11-14 at 14-28-31 Shrink relationComplexityError test size by jakebailey · Pull Request #62754 · microsoft_TypeScript.png</t>
+        </is>
+      </c>
+      <c r="C11" s="15" t="inlineStr">
+        <is>
+          <t>Files changed list under Copilot review summary</t>
+        </is>
+      </c>
+      <c r="D11" s="15" t="inlineStr">
+        <is>
+          <t>All 4 changed files are test artifacts: tests/cases/compiler/relationComplexityError.ts and three tests/baselines/reference/relationComplexityError.* baseline files — no production code touched.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="15" t="inlineStr">
+        <is>
+          <t>Testing is performed in accordance with the testing policy</t>
+        </is>
+      </c>
+      <c r="B12" s="15" t="inlineStr">
+        <is>
+          <t>Screenshot 2025-11-14 at 14-28-31 Shrink relationComplexityError test size by jakebailey · Pull Request #62754 · microsoft_TypeScript.png</t>
+        </is>
+      </c>
+      <c r="C12" s="15" t="inlineStr">
+        <is>
+          <t>Merge status footer</t>
+        </is>
+      </c>
+      <c r="D12" s="15" t="inlineStr">
+        <is>
+          <t>'36 of 37 checks passed' shown at merge; PR merged with status checks visible in the PR.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="15" t="inlineStr">
+        <is>
+          <t>Testing is performed in accordance with the testing policy</t>
+        </is>
+      </c>
+      <c r="B13" s="15" t="inlineStr">
         <is>
           <t>Screenshot 2025-11-14 at 14-29-21 Shrink relationComplexityError test size · microsoft_TypeScript@9e76dd2.png</t>
         </is>
       </c>
-      <c r="C7" s="16" t="inlineStr">
-        <is>
-          <t>Workflow trigger attribution</t>
-        </is>
-      </c>
-      <c r="D7" s="16" t="inlineStr">
-        <is>
-          <t>'jakebailey opened #62754' — confirms jakebailey as the author of the change; no indication RyanCavanaugh contributed commits.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="16" t="inlineStr">
+      <c r="C13" s="15" t="inlineStr">
+        <is>
+          <t>Workflow run header and Jobs list</t>
+        </is>
+      </c>
+      <c r="D13" s="15" t="inlineStr">
+        <is>
+          <t>CI workflow run #34653 tied to PR #62754 completed with Status: Success in 17m 44s. Jobs include coverage (12m 37s), lint, typecheck, smoke, baselines, browser-integration, and 15-job test matrix across Node 14–24 on Ubuntu/Windows/macOS — all green.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="15" t="inlineStr">
         <is>
           <t>Testing is performed in accordance with the testing policy</t>
         </is>
       </c>
-      <c r="B8" s="16" t="inlineStr">
+      <c r="B14" s="15" t="inlineStr">
         <is>
           <t>Screenshot 2025-11-14 at 14-29-21 Shrink relationComplexityError test size · microsoft_TypeScript@9e76dd2.png</t>
         </is>
       </c>
-      <c r="C8" s="16" t="inlineStr">
-        <is>
-          <t>Workflow run header and Jobs sidebar</t>
-        </is>
-      </c>
-      <c r="D8" s="16" t="inlineStr">
-        <is>
-          <t>CI workflow run #34653 on ci.yml triggered by PR #62754 completed with Success status in 17m 44s; 15 matrix test jobs across Node 14–24 on ubuntu/windows/macos all show green checks, plus coverage (12m 37s), lint, knip, format, typecheck, smoke, browser-integration, self-check and baselines jobs all green.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="16" t="inlineStr">
-        <is>
-          <t>Testing is performed in accordance with the testing policy</t>
-        </is>
-      </c>
-      <c r="B9" s="16" t="inlineStr">
-        <is>
-          <t>Screenshot 2025-11-14 at 14-28-31 Shrink relationComplexityError test size by jakebailey · Pull Request #62754 · microsoft_TypeScript.png</t>
-        </is>
-      </c>
-      <c r="C9" s="16" t="inlineStr">
-        <is>
-          <t>Checks summary in PR merge box</t>
-        </is>
-      </c>
-      <c r="D9" s="16" t="inlineStr">
-        <is>
-          <t>PR page shows '36 of 37' checks passed and PR was merged; test results were visible as PR status checks.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="16" t="inlineStr">
-        <is>
-          <t>Testing is performed in accordance with the testing policy</t>
-        </is>
-      </c>
-      <c r="B10" s="16" t="inlineStr">
-        <is>
-          <t>Screenshot 2025-11-14 at 14-27-50 Coverage Report.png</t>
-        </is>
-      </c>
-      <c r="C10" s="16" t="inlineStr">
-        <is>
-          <t>Summary row and Row 13 debug.ts</t>
-        </is>
-      </c>
-      <c r="D10" s="16" t="inlineStr">
-        <is>
-          <t>Aggregate coverage shows Statements 94.62%, Branches 89.48%, Functions 94.79% — above thresholds in aggregate — but Row 13 src/compiler/debug.ts is flagged red at Bytes 29.99% / Branches 19.28% / Functions 30.33%. No project name, commit SHA, branch, or timestamp is visible on the report to tie it to PR #62754.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="16" t="inlineStr">
-        <is>
-          <t>Testing is performed in accordance with the testing policy</t>
-        </is>
-      </c>
-      <c r="B11" s="16" t="inlineStr">
-        <is>
-          <t>Screenshot 2025-11-14 at 14-27-50 Coverage Report.png</t>
-        </is>
-      </c>
-      <c r="C11" s="16" t="inlineStr">
-        <is>
-          <t>Entire page - ambiguities noted</t>
-        </is>
-      </c>
-      <c r="D11" s="16" t="inlineStr">
-        <is>
-          <t>No pass/fail gate indicator, no author/reviewer attribution, and no linkage to a specific PR/build. Cannot confirm this report was generated for and reviewed as part of PR #62754.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="16" t="inlineStr">
-        <is>
-          <t>Testing is performed in accordance with the testing policy</t>
-        </is>
-      </c>
-      <c r="B12" s="16" t="inlineStr">
-        <is>
-          <t>Screenshot 2025-11-14 at 14-28-31 Shrink relationComplexityError test size by jakebailey · Pull Request #62754 · microsoft_TypeScript.png</t>
-        </is>
-      </c>
-      <c r="C12" s="16" t="inlineStr">
-        <is>
-          <t>PR header stats</t>
-        </is>
-      </c>
-      <c r="D12" s="16" t="inlineStr">
-        <is>
-          <t>PR is 4 files changed, +10/-10 (a small test-size reduction per title 'Shrink relationComplexityError test size'). No security scan review evidence and no manual smoke test sign-off visible.</t>
+      <c r="C14" s="15" t="inlineStr">
+        <is>
+          <t>Artifacts section</t>
+        </is>
+      </c>
+      <c r="D14" s="15" t="inlineStr">
+        <is>
+          <t>A 'coverage' artifact (39.2 MB) was produced by the CI run, evidencing coverage report generation as part of the pipeline.</t>
         </is>
       </c>
     </row>
@@ -1264,104 +1286,104 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="15" t="inlineStr">
+      <c r="A1" s="14" t="inlineStr">
         <is>
           <t>File</t>
         </is>
       </c>
-      <c r="B1" s="15" t="inlineStr">
+      <c r="B1" s="14" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="C1" s="15" t="inlineStr">
+      <c r="C1" s="14" t="inlineStr">
         <is>
           <t>Size (bytes)</t>
         </is>
       </c>
-      <c r="D1" s="15" t="inlineStr">
+      <c r="D1" s="14" t="inlineStr">
         <is>
           <t>Extraction summary</t>
         </is>
       </c>
-      <c r="E1" s="15" t="inlineStr">
+      <c r="E1" s="14" t="inlineStr">
         <is>
           <t>Cited by attributes</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="16" t="inlineStr">
+      <c r="A2" s="15" t="inlineStr">
         <is>
           <t>Screenshot 2025-11-14 at 14-27-50 Coverage Report.png</t>
         </is>
       </c>
-      <c r="B2" s="16" t="inlineStr">
+      <c r="B2" s="15" t="inlineStr">
         <is>
           <t>screenshot</t>
         </is>
       </c>
-      <c r="C2" s="16" t="n">
+      <c r="C2" s="15" t="n">
         <v>840334</v>
       </c>
-      <c r="D2" s="16" t="inlineStr">
-        <is>
-          <t>Coverage report dashboard · 14 facts extracted · 6 ambiguity flag(s)</t>
-        </is>
-      </c>
-      <c r="E2" s="16" t="inlineStr">
-        <is>
-          <t>testing-per-policy, testing-per-policy</t>
+      <c r="D2" s="15" t="inlineStr">
+        <is>
+          <t>Coverage report dashboard · 13 facts extracted · 5 ambiguity flag(s)</t>
+        </is>
+      </c>
+      <c r="E2" s="15" t="inlineStr">
+        <is>
+          <t>testing-per-testing-policy</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="16" t="inlineStr">
+      <c r="A3" s="15" t="inlineStr">
         <is>
           <t>Screenshot 2025-11-14 at 14-28-31 Shrink relationComplexityError test size by jakebailey · Pull Request #62754 · microsoft_TypeScript.png</t>
         </is>
       </c>
-      <c r="B3" s="16" t="inlineStr">
+      <c r="B3" s="15" t="inlineStr">
         <is>
           <t>screenshot</t>
         </is>
       </c>
-      <c r="C3" s="16" t="n">
+      <c r="C3" s="15" t="n">
         <v>1589450</v>
       </c>
-      <c r="D3" s="16" t="inlineStr">
-        <is>
-          <t>GitHub Pull Request page (Conversation tab) · 1 facts extracted · 4 ambiguity flag(s)</t>
-        </is>
-      </c>
-      <c r="E3" s="16" t="inlineStr">
-        <is>
-          <t>code-review-prior-to-main-merge, code-review-prior-to-main-merge, code-review-prior-to-main-merge, independent-reviewer-approval, independent-reviewer-approval, testing-per-policy, testing-per-policy</t>
+      <c r="D3" s="15" t="inlineStr">
+        <is>
+          <t>GitHub Pull Request page (Conversation tab) · 1 facts extracted · 7 people · 4 ambiguity flag(s)</t>
+        </is>
+      </c>
+      <c r="E3" s="15" t="inlineStr">
+        <is>
+          <t>code-review-before-merge-to-main, code-review-before-merge-to-main, code-review-before-merge-to-main, code-review-before-merge-to-main, independent-reviewer-approval, independent-reviewer-approval, independent-reviewer-approval, independent-reviewer-approval, testing-per-testing-policy, testing-per-testing-policy</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="16" t="inlineStr">
+      <c r="A4" s="15" t="inlineStr">
         <is>
           <t>Screenshot 2025-11-14 at 14-29-21 Shrink relationComplexityError test size · microsoft_TypeScript@9e76dd2.png</t>
         </is>
       </c>
-      <c r="B4" s="16" t="inlineStr">
+      <c r="B4" s="15" t="inlineStr">
         <is>
           <t>screenshot</t>
         </is>
       </c>
-      <c r="C4" s="16" t="n">
+      <c r="C4" s="15" t="n">
         <v>705765</v>
       </c>
-      <c r="D4" s="16" t="inlineStr">
-        <is>
-          <t>GitHub Actions workflow run summary · 18 facts extracted · 1 people · 4 ambiguity flag(s)</t>
-        </is>
-      </c>
-      <c r="E4" s="16" t="inlineStr">
-        <is>
-          <t>independent-reviewer-approval, testing-per-policy</t>
+      <c r="D4" s="15" t="inlineStr">
+        <is>
+          <t>GitHub Actions workflow run summary · 1 facts extracted · 1 people · 5 ambiguity flag(s)</t>
+        </is>
+      </c>
+      <c r="E4" s="15" t="inlineStr">
+        <is>
+          <t>testing-per-testing-policy, testing-per-testing-policy</t>
         </is>
       </c>
     </row>
@@ -1376,7 +1398,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1391,461 +1413,321 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="15" t="inlineStr">
+      <c r="A1" s="14" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B1" s="15" t="inlineStr">
+      <c r="B1" s="14" t="inlineStr">
         <is>
           <t>Timestamp</t>
         </is>
       </c>
-      <c r="C1" s="15" t="inlineStr">
+      <c r="C1" s="14" t="inlineStr">
         <is>
           <t>Purpose</t>
         </is>
       </c>
-      <c r="D1" s="15" t="inlineStr">
+      <c r="D1" s="14" t="inlineStr">
         <is>
           <t>Model</t>
         </is>
       </c>
-      <c r="E1" s="15" t="inlineStr">
+      <c r="E1" s="14" t="inlineStr">
         <is>
           <t>Input tokens</t>
         </is>
       </c>
-      <c r="F1" s="15" t="inlineStr">
+      <c r="F1" s="14" t="inlineStr">
         <is>
           <t>Cache read</t>
         </is>
       </c>
-      <c r="G1" s="15" t="inlineStr">
+      <c r="G1" s="14" t="inlineStr">
         <is>
           <t>Output tokens</t>
         </is>
       </c>
-      <c r="H1" s="15" t="inlineStr">
+      <c r="H1" s="14" t="inlineStr">
         <is>
           <t>Cost USD</t>
         </is>
       </c>
-      <c r="I1" s="15" t="inlineStr">
+      <c r="I1" s="14" t="inlineStr">
         <is>
           <t>Latency (ms)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="16" t="n">
+      <c r="A2" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="16" t="inlineStr">
-        <is>
-          <t>2026-07-03T03:12:13.509632Z</t>
-        </is>
-      </c>
-      <c r="C2" s="16" t="inlineStr">
+      <c r="B2" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-03T03:32:12.174534Z</t>
+        </is>
+      </c>
+      <c r="C2" s="15" t="inlineStr">
         <is>
           <t>screenshot:Screenshot 2025-11-14 at 14-27-50 Coverage Report.png</t>
         </is>
       </c>
-      <c r="D2" s="16" t="inlineStr">
+      <c r="D2" s="15" t="inlineStr">
         <is>
           <t>claude-opus-4-7</t>
         </is>
       </c>
-      <c r="E2" s="16" t="n">
+      <c r="E2" s="15" t="n">
         <v>6675</v>
       </c>
-      <c r="F2" s="16" t="n">
+      <c r="F2" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="G2" s="16" t="n">
-        <v>1407</v>
-      </c>
-      <c r="H2" s="19" t="n">
-        <v>0.20565</v>
-      </c>
-      <c r="I2" s="16" t="n">
-        <v>20042</v>
+      <c r="G2" s="15" t="n">
+        <v>1441</v>
+      </c>
+      <c r="H2" s="17" t="n">
+        <v>0.2082</v>
+      </c>
+      <c r="I2" s="15" t="n">
+        <v>20593</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="16" t="n">
+      <c r="A3" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="16" t="inlineStr">
-        <is>
-          <t>2026-07-03T03:12:27.884788Z</t>
-        </is>
-      </c>
-      <c r="C3" s="16" t="inlineStr">
+      <c r="B3" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-03T03:32:37.674329Z</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
         <is>
           <t>screenshot:Screenshot 2025-11-14 at 14-28-31 Shrink relationComplexityError test size by jakebailey · Pull Request #62754 · microsoft_TypeScript.png</t>
         </is>
       </c>
-      <c r="D3" s="16" t="inlineStr">
+      <c r="D3" s="15" t="inlineStr">
         <is>
           <t>claude-opus-4-7</t>
         </is>
       </c>
-      <c r="E3" s="16" t="n">
+      <c r="E3" s="15" t="n">
         <v>7348</v>
       </c>
-      <c r="F3" s="16" t="n">
+      <c r="F3" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="G3" s="16" t="n">
-        <v>881</v>
-      </c>
-      <c r="H3" s="19" t="n">
-        <v>0.176295</v>
-      </c>
-      <c r="I3" s="16" t="n">
-        <v>14360</v>
+      <c r="G3" s="15" t="n">
+        <v>1903</v>
+      </c>
+      <c r="H3" s="17" t="n">
+        <v>0.252945</v>
+      </c>
+      <c r="I3" s="15" t="n">
+        <v>25488</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="16" t="n">
+      <c r="A4" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="16" t="inlineStr">
-        <is>
-          <t>2026-07-03T03:12:50.407995Z</t>
-        </is>
-      </c>
-      <c r="C4" s="16" t="inlineStr">
+      <c r="B4" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-03T03:33:00.969443Z</t>
+        </is>
+      </c>
+      <c r="C4" s="15" t="inlineStr">
         <is>
           <t>screenshot:Screenshot 2025-11-14 at 14-29-21 Shrink relationComplexityError test size · microsoft_TypeScript@9e76dd2.png</t>
         </is>
       </c>
-      <c r="D4" s="16" t="inlineStr">
+      <c r="D4" s="15" t="inlineStr">
         <is>
           <t>claude-opus-4-7</t>
         </is>
       </c>
-      <c r="E4" s="16" t="n">
+      <c r="E4" s="15" t="n">
         <v>7300</v>
       </c>
-      <c r="F4" s="16" t="n">
+      <c r="F4" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="G4" s="16" t="n">
-        <v>1515</v>
-      </c>
-      <c r="H4" s="19" t="n">
-        <v>0.223125</v>
-      </c>
-      <c r="I4" s="16" t="n">
-        <v>22513</v>
+      <c r="G4" s="15" t="n">
+        <v>1556</v>
+      </c>
+      <c r="H4" s="17" t="n">
+        <v>0.2262</v>
+      </c>
+      <c r="I4" s="15" t="n">
+        <v>23287</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="16" t="n">
+      <c r="A5" s="15" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="16" t="inlineStr">
-        <is>
-          <t>2026-07-03T03:13:03.363074Z</t>
-        </is>
-      </c>
-      <c r="C5" s="16" t="inlineStr">
-        <is>
-          <t>judge:code-review-prior-to-main-merge:sample-1</t>
-        </is>
-      </c>
-      <c r="D5" s="16" t="inlineStr">
+      <c r="B5" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-03T03:33:40.675628Z</t>
+        </is>
+      </c>
+      <c r="C5" s="15" t="inlineStr">
+        <is>
+          <t>judge:code-review-before-merge-to-main:sample-1</t>
+        </is>
+      </c>
+      <c r="D5" s="15" t="inlineStr">
         <is>
           <t>claude-opus-4-7</t>
         </is>
       </c>
-      <c r="E5" s="16" t="n">
-        <v>4675</v>
-      </c>
-      <c r="F5" s="16" t="n">
-        <v>2638</v>
-      </c>
-      <c r="G5" s="16" t="n">
-        <v>945</v>
-      </c>
-      <c r="H5" s="19" t="n">
-        <v>0.105387</v>
-      </c>
-      <c r="I5" s="16" t="n">
-        <v>12944</v>
+      <c r="E5" s="15" t="n">
+        <v>17781</v>
+      </c>
+      <c r="F5" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="15" t="n">
+        <v>3199</v>
+      </c>
+      <c r="H5" s="17" t="n">
+        <v>0.50664</v>
+      </c>
+      <c r="I5" s="15" t="n">
+        <v>14174</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="16" t="n">
+      <c r="A6" s="15" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>2026-07-03T03:13:16.199623Z</t>
-        </is>
-      </c>
-      <c r="C6" s="16" t="inlineStr">
+      <c r="B6" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-03T03:34:20.967393Z</t>
+        </is>
+      </c>
+      <c r="C6" s="15" t="inlineStr">
         <is>
           <t>judge:independent-reviewer-approval:sample-1</t>
         </is>
       </c>
-      <c r="D6" s="16" t="inlineStr">
+      <c r="D6" s="15" t="inlineStr">
         <is>
           <t>claude-opus-4-7</t>
         </is>
       </c>
-      <c r="E6" s="16" t="n">
-        <v>4648</v>
-      </c>
-      <c r="F6" s="16" t="n">
-        <v>2638</v>
-      </c>
-      <c r="G6" s="16" t="n">
-        <v>998</v>
-      </c>
-      <c r="H6" s="19" t="n">
-        <v>0.108957</v>
-      </c>
-      <c r="I6" s="16" t="n">
-        <v>12834</v>
+      <c r="E6" s="15" t="n">
+        <v>17817</v>
+      </c>
+      <c r="F6" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="15" t="n">
+        <v>3171</v>
+      </c>
+      <c r="H6" s="17" t="n">
+        <v>0.50508</v>
+      </c>
+      <c r="I6" s="15" t="n">
+        <v>13992</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="16" t="n">
+      <c r="A7" s="15" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="16" t="inlineStr">
-        <is>
-          <t>2026-07-03T03:13:41.442272Z</t>
-        </is>
-      </c>
-      <c r="C7" s="16" t="inlineStr">
-        <is>
-          <t>judge:testing-per-policy:sample-1</t>
-        </is>
-      </c>
-      <c r="D7" s="16" t="inlineStr">
+      <c r="B7" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-03T03:35:30.646658Z</t>
+        </is>
+      </c>
+      <c r="C7" s="15" t="inlineStr">
+        <is>
+          <t>judge:testing-per-testing-policy:sample-1</t>
+        </is>
+      </c>
+      <c r="D7" s="15" t="inlineStr">
         <is>
           <t>claude-opus-4-7</t>
         </is>
       </c>
-      <c r="E7" s="16" t="n">
-        <v>6393</v>
-      </c>
-      <c r="F7" s="16" t="n">
-        <v>2638</v>
-      </c>
-      <c r="G7" s="16" t="n">
-        <v>1944</v>
-      </c>
-      <c r="H7" s="19" t="n">
-        <v>0.206082</v>
-      </c>
-      <c r="I7" s="16" t="n">
-        <v>25240</v>
+      <c r="E7" s="15" t="n">
+        <v>23199</v>
+      </c>
+      <c r="F7" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="15" t="n">
+        <v>5402</v>
+      </c>
+      <c r="H7" s="17" t="n">
+        <v>0.753135</v>
+      </c>
+      <c r="I7" s="15" t="n">
+        <v>26173</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="16" t="n">
+      <c r="A8" s="15" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="16" t="inlineStr">
-        <is>
-          <t>2026-07-03T03:14:05.324278Z</t>
-        </is>
-      </c>
-      <c r="C8" s="16" t="inlineStr">
+      <c r="B8" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-03T03:35:54.379157Z</t>
+        </is>
+      </c>
+      <c r="C8" s="15" t="inlineStr">
         <is>
           <t>screenshot:Screenshot 2025-11-14 at 14-31-38 feat use Node.js timers by default · denoland_deno@12cde71.png</t>
         </is>
       </c>
-      <c r="D8" s="16" t="inlineStr">
+      <c r="D8" s="15" t="inlineStr">
         <is>
           <t>claude-opus-4-7</t>
         </is>
       </c>
-      <c r="E8" s="16" t="n">
+      <c r="E8" s="15" t="n">
         <v>7264</v>
       </c>
-      <c r="F8" s="16" t="n">
+      <c r="F8" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="G8" s="16" t="n">
-        <v>1687</v>
-      </c>
-      <c r="H8" s="19" t="n">
-        <v>0.235485</v>
-      </c>
-      <c r="I8" s="16" t="n">
-        <v>23872</v>
+      <c r="G8" s="15" t="n">
+        <v>1605</v>
+      </c>
+      <c r="H8" s="17" t="n">
+        <v>0.229335</v>
+      </c>
+      <c r="I8" s="15" t="n">
+        <v>23722</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="16" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" s="16" t="inlineStr">
-        <is>
-          <t>2026-07-03T03:14:29.583419Z</t>
-        </is>
-      </c>
-      <c r="C9" s="16" t="inlineStr">
-        <is>
-          <t>screenshot:Screenshot 2025-11-14 at 14-32-05 feat use Node.js timers by default by bartlomieju · Pull Request #31272 · denoland_deno.png</t>
-        </is>
-      </c>
-      <c r="D9" s="16" t="inlineStr">
-        <is>
-          <t>claude-opus-4-7</t>
-        </is>
-      </c>
-      <c r="E9" s="16" t="n">
-        <v>7295</v>
-      </c>
-      <c r="F9" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" s="16" t="n">
-        <v>1754</v>
-      </c>
-      <c r="H9" s="19" t="n">
-        <v>0.240975</v>
-      </c>
-      <c r="I9" s="16" t="n">
-        <v>24265</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="16" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" s="16" t="inlineStr">
-        <is>
-          <t>2026-07-03T03:14:42.378276Z</t>
-        </is>
-      </c>
-      <c r="C10" s="16" t="inlineStr">
-        <is>
-          <t>judge:code-review-prior-to-main-merge:sample-2</t>
-        </is>
-      </c>
-      <c r="D10" s="16" t="inlineStr">
-        <is>
-          <t>claude-opus-4-7</t>
-        </is>
-      </c>
-      <c r="E10" s="16" t="n">
-        <v>4299</v>
-      </c>
-      <c r="F10" s="16" t="n">
-        <v>2638</v>
-      </c>
-      <c r="G10" s="16" t="n">
-        <v>1055</v>
-      </c>
-      <c r="H10" s="19" t="n">
-        <v>0.107997</v>
-      </c>
-      <c r="I10" s="16" t="n">
-        <v>12795</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="16" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" s="16" t="inlineStr">
-        <is>
-          <t>2026-07-03T03:14:55.046889Z</t>
-        </is>
-      </c>
-      <c r="C11" s="16" t="inlineStr">
-        <is>
-          <t>judge:independent-reviewer-approval:sample-2</t>
-        </is>
-      </c>
-      <c r="D11" s="16" t="inlineStr">
-        <is>
-          <t>claude-opus-4-7</t>
-        </is>
-      </c>
-      <c r="E11" s="16" t="n">
-        <v>4272</v>
-      </c>
-      <c r="F11" s="16" t="n">
-        <v>2638</v>
-      </c>
-      <c r="G11" s="16" t="n">
-        <v>1101</v>
-      </c>
-      <c r="H11" s="19" t="n">
-        <v>0.111042</v>
-      </c>
-      <c r="I11" s="16" t="n">
-        <v>12667</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="16" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" s="16" t="inlineStr">
-        <is>
-          <t>2026-07-03T03:15:16.003233Z</t>
-        </is>
-      </c>
-      <c r="C12" s="16" t="inlineStr">
-        <is>
-          <t>judge:testing-per-policy:sample-2</t>
-        </is>
-      </c>
-      <c r="D12" s="16" t="inlineStr">
-        <is>
-          <t>claude-opus-4-7</t>
-        </is>
-      </c>
-      <c r="E12" s="16" t="n">
-        <v>6017</v>
-      </c>
-      <c r="F12" s="16" t="n">
-        <v>2638</v>
-      </c>
-      <c r="G12" s="16" t="n">
-        <v>1616</v>
-      </c>
-      <c r="H12" s="19" t="n">
-        <v>0.175842</v>
-      </c>
-      <c r="I12" s="16" t="n">
-        <v>20956</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="C13" s="20" t="inlineStr">
+      <c r="C9" s="18" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="E13" s="20">
-        <f>SUM(E2:E12)</f>
+      <c r="E9" s="18">
+        <f>SUM(E2:E8)</f>
         <v/>
       </c>
-      <c r="F13" s="20">
-        <f>SUM(F2:F12)</f>
+      <c r="F9" s="18">
+        <f>SUM(F2:F8)</f>
         <v/>
       </c>
-      <c r="G13" s="20">
-        <f>SUM(G2:G12)</f>
+      <c r="G9" s="18">
+        <f>SUM(G2:G8)</f>
         <v/>
       </c>
-      <c r="H13" s="21">
-        <f>SUM(H2:H12)</f>
+      <c r="H9" s="19">
+        <f>SUM(H2:H8)</f>
         <v/>
       </c>
-      <c r="I13" s="20">
-        <f>SUM(I2:I12)</f>
+      <c r="I9" s="18">
+        <f>SUM(I2:I8)</f>
         <v/>
       </c>
     </row>

--- a/output/independent-code-review/claude/sample-1/workpaper.xlsx
+++ b/output/independent-code-review/claude/sample-1/workpaper.xlsx
@@ -645,7 +645,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>03 Jul 2026, 03:35 UTC</t>
+          <t>03 Jul 2026, 03:49 UTC</t>
         </is>
       </c>
     </row>
@@ -863,19 +863,19 @@
         </is>
       </c>
       <c r="C2" s="15" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="D2" s="15" t="inlineStr">
         <is>
-          <t>A pull request record (PR #62754) exists for the change, and RyanCavanaugh approved the PR 17 hours ago while the merge into microsoft:main occurred 16 hours ago — approval precedes merge. The PR shows a 'Merged' badge and the footer confirms the branch was merged via PR (not a direct push to main). This attribute concerns existence and timing of review vs merge; reviewer independence is a separate attribute.</t>
+          <t>A pull request (#62754) exists for the change and shows a human approval from RyanCavanaugh recorded at "17 hours ago", while the merge to microsoft:main occurred "16 hours ago" — i.e. the approval preceded the merge. The PR page shows the change was merged via the PR (merge commit ea48ded into microsoft:main), not committed directly to main, satisfying the 4-eyes / no-direct-commit criterion for this attribute. Independence of the reviewer is a separate attribute and is not judged here.</t>
         </is>
       </c>
       <c r="E2" s="15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F2" s="15" t="inlineStr">
         <is>
-          <t>Reviewer independence (Copilot AI reviewer is not an independent human) is not in scope for this attribute — this attribute tests timing/existence of a code review before merge, which is satisfied by RyanCavanaugh's human approval prior to merge.</t>
+          <t>Copilot AI review — not counted toward this attribute since the human approval by RyanCavanaugh already satisfies the 'code review completed before merge' criterion; independence of reviewer is judged under a separate attribute.</t>
         </is>
       </c>
     </row>
@@ -895,7 +895,7 @@
       </c>
       <c r="D3" s="15" t="inlineStr">
         <is>
-          <t>The PR #62754 was authored and merged by jakebailey, and shows an approving review from RyanCavanaugh (a different named human), documented in the GitHub Reviewers sidebar with a green check. Copilot's review is explicitly not counted as an independent human review, but RyanCavanaugh's approval satisfies the 4-eyes requirement. There is no indication RyanCavanaugh committed or co-authored the change (author/committer/assignee are all jakebailey), and the merge was not a self-approval since a separate approver granted the required review.</t>
+          <t>The PR was authored and merged by jakebailey, and the approving reviewer is RyanCavanaugh — a different named human — whose approval (green check) is recorded in the timeline prior to the merge event. Copilot's review is not counted as an independent human approval, but RyanCavanaugh's approval satisfies the 4-eyes requirement on its own. No evidence indicates RyanCavanaugh committed or co-authored the change (single commit 9e76dd2 attributed to jakebailey).</t>
         </is>
       </c>
       <c r="E3" s="15" t="n">
@@ -903,7 +903,7 @@
       </c>
       <c r="F3" s="15" t="inlineStr">
         <is>
-          <t>Copilot as reviewer — rejected as an independent human reviewer per guidance; however RyanCavanaugh provides the required independent human approval so the criterion is still met.</t>
+          <t>Copilot AI review — rejected as an independent reviewer because it is not a human; however RyanCavanaugh provides an independent human approval, so the criterion is still met.</t>
         </is>
       </c>
     </row>
@@ -923,16 +923,16 @@
       </c>
       <c r="D4" s="15" t="inlineStr">
         <is>
-          <t>The change is a test-only reduction (shrinks the Digits type in a compiler relationComplexityError test from 10 to 8 literals), affecting only test files under tests/cases and tests/baselines — a behavior-preserving test refactor rather than production logic. The CI pipeline ran successfully (Success, 17m 44s, 36 of 37 checks passed) including coverage, lint, typecheck, smoke, baselines, and multi-OS/multi-Node matrix jobs, with a coverage artifact produced. The coverage report shows repository-wide metrics well above policy thresholds: Statements 94.62%, Branches 89.48% (≥70%), Functions 94.79% (≥80%). Test results are visible in PR status checks and were executed pre-merge. No security/payment/auth flows are touched. Criteria are met on the evidence available.</t>
+          <t>The change is a test-size reduction (+10/-10 in a test file, "Shrink relationComplexityError test size"), which is a behavior-preserving refactor of test code — an exception category under the policy, but even without invoking it the coverage report shows Statements 94.62%, Branches 89.48%, Functions 94.79% (all above the 80%/70%/80% thresholds). CI ran the full test matrix (15 jobs across Node 14–24, coverage, lint, knip, format, browser-integration, typecheck, smoke, baselines) with status Success and 36 of 37 checks passed, and results are visible as PR status checks. A coverage report artifact (39.2 MB) was generated by the coverage job and a coverage dashboard screenshot was captured as part of the review. No line-coverage percentage is directly shown (only Bytes/Statements/Branches/Functions) but Statements is the standard proxy and comfortably exceeds 80%.</t>
         </is>
       </c>
       <c r="E4" s="15" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F4" s="15" t="inlineStr">
         <is>
-          <t>Refactoring with No Behavioral Changes: Accepted as applicable — the PR modifies only test source and baseline reference files to reduce test complexity/runtime ('Getting tired of this test timing out on slower builders'), with no production code changes. Existing test coverage in CI verifies behavior.
-Coverage report not tied by commit SHA/PR to this specific change on the report page — noted as an ambiguity, but the CI run for commit 9e76dd2 produced a coverage artifact and the repository-wide coverage metrics all exceed thresholds, so this does not overturn SUCCESS.</t>
+          <t>Refactoring with No Behavioral Changes: the PR shrinks the size of an existing test (relationComplexityError) to avoid timeouts on slower builders — behavior-preserving test refactor. Accepted as applicable, though not required because measured coverage already exceeds thresholds.
+Line coverage column is not shown in the coverage report (only Bytes/Statements/Branches/Functions). Statements coverage 94.62% is treated as the practical equivalent for the 80% line-coverage criterion; noted as a minor ambiguity but not fatal given the large margin above threshold.</t>
         </is>
       </c>
     </row>
@@ -947,7 +947,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -991,12 +991,12 @@
       </c>
       <c r="C2" s="15" t="inlineStr">
         <is>
-          <t>PR header / Merged badge</t>
+          <t>PR header and Merged status badge</t>
         </is>
       </c>
       <c r="D2" s="15" t="inlineStr">
         <is>
-          <t>Purple 'Merged' badge and header 'jakebailey merged 1 commit into microsoft:main from jakebailey:relationComplexityErrorSmaller 16 hours ago' — confirms PR record exists and was merged to main.</t>
+          <t>PR #62754 exists in microsoft/TypeScript with status 'Merged'; header states 'jakebailey merged 1 commit into microsoft:main from jakebailey:relationComplexityErrorSmaller 16 hours ago'.</t>
         </is>
       </c>
     </row>
@@ -1013,12 +1013,12 @@
       </c>
       <c r="C3" s="15" t="inlineStr">
         <is>
-          <t>Timeline event (approval)</t>
+          <t>Timeline — approval event</t>
         </is>
       </c>
       <c r="D3" s="15" t="inlineStr">
         <is>
-          <t>'RyanCavanaugh approved these changes 17 hours ago' — approval timestamp precedes the merge timestamp (16 hours ago).</t>
+          <t>'RyanCavanaugh approved these changes 17 hours ago' with a green check, and Reviewers sidebar shows RyanCavanaugh with a green check.</t>
         </is>
       </c>
     </row>
@@ -1035,19 +1035,19 @@
       </c>
       <c r="C4" s="15" t="inlineStr">
         <is>
-          <t>Merge timeline event</t>
+          <t>Merge event line</t>
         </is>
       </c>
       <c r="D4" s="15" t="inlineStr">
         <is>
-          <t>'jakebailey merged commit ea48ded into microsoft:main 16 hours ago' — merge into main occurred after the approval one hour earlier.</t>
+          <t>'jakebailey merged commit ea48ded into microsoft:main 16 hours ago' — merge occurred one hour after the approval, i.e. after approval was recorded.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="15" t="inlineStr">
         <is>
-          <t>Code Reviews are performed prior to committing a change to the main branch</t>
+          <t>Code Review approvals are performed by independent code reviewers</t>
         </is>
       </c>
       <c r="B5" s="15" t="inlineStr">
@@ -1057,12 +1057,12 @@
       </c>
       <c r="C5" s="15" t="inlineStr">
         <is>
-          <t>Footer banner</t>
+          <t>PR header</t>
         </is>
       </c>
       <c r="D5" s="15" t="inlineStr">
         <is>
-          <t>'Pull request successfully merged and closed — the branch has been merged.' confirms change reached main via reviewed PR, not direct commit.</t>
+          <t>'jakebailey merged 1 commit into microsoft:main from jakebailey:relationComplexityErrorSmaller' — identifies jakebailey as both author and merger.</t>
         </is>
       </c>
     </row>
@@ -1079,12 +1079,12 @@
       </c>
       <c r="C6" s="15" t="inlineStr">
         <is>
-          <t>Timeline event, mid-page</t>
+          <t>Timeline — approval event</t>
         </is>
       </c>
       <c r="D6" s="15" t="inlineStr">
         <is>
-          <t>'RyanCavanaugh approved these changes 17 hours ago' with green check and 'View reviewed changes' link.</t>
+          <t>'RyanCavanaugh approved these changes 17 hours ago' with green check, occurring before the merge event 16 hours ago.</t>
         </is>
       </c>
     </row>
@@ -1101,12 +1101,12 @@
       </c>
       <c r="C7" s="15" t="inlineStr">
         <is>
-          <t>PR header</t>
+          <t>Reviewers sidebar</t>
         </is>
       </c>
       <c r="D7" s="15" t="inlineStr">
         <is>
-          <t>'jakebailey merged 1 commit into microsoft:main from jakebailey:relationComplexityErrorSmaller' — identifies jakebailey as author and merger.</t>
+          <t>RyanCavanaugh listed with green check (✓); Copilot listed without a check — Copilot is a bot, not an independent human reviewer.</t>
         </is>
       </c>
     </row>
@@ -1123,34 +1123,34 @@
       </c>
       <c r="C8" s="15" t="inlineStr">
         <is>
-          <t>Right sidebar — Reviewers panel</t>
+          <t>Commit reference in timeline</t>
         </is>
       </c>
       <c r="D8" s="15" t="inlineStr">
         <is>
-          <t>Reviewers listed: Copilot and RyanCavanaugh, with green check next to RyanCavanaugh indicating approval; Assignees: jakebailey.</t>
+          <t>Single commit 9e76dd2 for 'Shrink_relationComplexityError_test_size' is associated with the PR (authored by jakebailey per branch context); no indication RyanCavanaugh co-authored or committed.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="15" t="inlineStr">
         <is>
-          <t>Code Review approvals are performed by independent code reviewers</t>
+          <t>Testing is performed in accordance with the testing policy</t>
         </is>
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>Screenshot 2025-11-14 at 14-28-31 Shrink relationComplexityError test size by jakebailey · Pull Request #62754 · microsoft_TypeScript.png</t>
+          <t>Screenshot 2025-11-14 at 14-27-50 Coverage Report.png</t>
         </is>
       </c>
       <c r="C9" s="15" t="inlineStr">
         <is>
-          <t>Merge status banner near bottom</t>
+          <t>Summary row (top of table)</t>
         </is>
       </c>
       <c r="D9" s="15" t="inlineStr">
         <is>
-          <t>'jakebailey merged commit ea48ded into microsoft:main 16 hours ago' — confirms merge occurred after RyanCavanaugh's approval was recorded.</t>
+          <t>Statements 94.62%, Branches 89.48%, Functions 94.79% — all above policy thresholds of 80/70/80.</t>
         </is>
       </c>
     </row>
@@ -1162,17 +1162,17 @@
       </c>
       <c r="B10" s="15" t="inlineStr">
         <is>
-          <t>Screenshot 2025-11-14 at 14-27-50 Coverage Report.png</t>
+          <t>Screenshot 2025-11-14 at 14-29-21 Shrink relationComplexityError test size · microsoft_TypeScript@9e76dd2.png</t>
         </is>
       </c>
       <c r="C10" s="15" t="inlineStr">
         <is>
-          <t>Summary row (top of coverage table)</t>
+          <t>Workflow run header and Jobs sidebar</t>
         </is>
       </c>
       <c r="D10" s="15" t="inlineStr">
         <is>
-          <t>Statements 94.62%, Branches 89.48%, Functions 94.79%, Bytes 95.96% — all above policy thresholds (statements ≥80, branches ≥70, functions ≥80).</t>
+          <t>CI run #34653 status Success, 17m 44s, 15 matrix jobs plus coverage/lint/knip/format/browser-integration/typecheck/smoke/baselines all green; coverage artifact 39.2 MB produced.</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="C11" s="15" t="inlineStr">
         <is>
-          <t>Files changed list under Copilot review summary</t>
+          <t>Merge status bar / checks summary</t>
         </is>
       </c>
       <c r="D11" s="15" t="inlineStr">
         <is>
-          <t>All 4 changed files are test artifacts: tests/cases/compiler/relationComplexityError.ts and three tests/baselines/reference/relationComplexityError.* baseline files — no production code touched.</t>
+          <t>'36 of 37 checks passed' shown on the merged PR; PR title 'Shrink relationComplexityError test size', +10/-10 across 4 files — a test-shrinking refactor.</t>
         </is>
       </c>
     </row>
@@ -1206,61 +1206,17 @@
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>Screenshot 2025-11-14 at 14-28-31 Shrink relationComplexityError test size by jakebailey · Pull Request #62754 · microsoft_TypeScript.png</t>
+          <t>Screenshot 2025-11-14 at 14-27-50 Coverage Report.png</t>
         </is>
       </c>
       <c r="C12" s="15" t="inlineStr">
         <is>
-          <t>Merge status footer</t>
+          <t>Page header</t>
         </is>
       </c>
       <c r="D12" s="15" t="inlineStr">
         <is>
-          <t>'36 of 37 checks passed' shown at merge; PR merged with status checks visible in the PR.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="15" t="inlineStr">
-        <is>
-          <t>Testing is performed in accordance with the testing policy</t>
-        </is>
-      </c>
-      <c r="B13" s="15" t="inlineStr">
-        <is>
-          <t>Screenshot 2025-11-14 at 14-29-21 Shrink relationComplexityError test size · microsoft_TypeScript@9e76dd2.png</t>
-        </is>
-      </c>
-      <c r="C13" s="15" t="inlineStr">
-        <is>
-          <t>Workflow run header and Jobs list</t>
-        </is>
-      </c>
-      <c r="D13" s="15" t="inlineStr">
-        <is>
-          <t>CI workflow run #34653 tied to PR #62754 completed with Status: Success in 17m 44s. Jobs include coverage (12m 37s), lint, typecheck, smoke, baselines, browser-integration, and 15-job test matrix across Node 14–24 on Ubuntu/Windows/macOS — all green.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="15" t="inlineStr">
-        <is>
-          <t>Testing is performed in accordance with the testing policy</t>
-        </is>
-      </c>
-      <c r="B14" s="15" t="inlineStr">
-        <is>
-          <t>Screenshot 2025-11-14 at 14-29-21 Shrink relationComplexityError test size · microsoft_TypeScript@9e76dd2.png</t>
-        </is>
-      </c>
-      <c r="C14" s="15" t="inlineStr">
-        <is>
-          <t>Artifacts section</t>
-        </is>
-      </c>
-      <c r="D14" s="15" t="inlineStr">
-        <is>
-          <t>A 'coverage' artifact (39.2 MB) was produced by the CI run, evidencing coverage report generation as part of the pipeline.</t>
+          <t>'Coverage Report' dashboard was generated and captured, evidencing that a coverage report exists for review.</t>
         </is>
       </c>
     </row>
@@ -1328,12 +1284,12 @@
       </c>
       <c r="D2" s="15" t="inlineStr">
         <is>
-          <t>Coverage report dashboard · 13 facts extracted · 5 ambiguity flag(s)</t>
+          <t>Coverage report dashboard · 1 facts extracted · 6 ambiguity flag(s)</t>
         </is>
       </c>
       <c r="E2" s="15" t="inlineStr">
         <is>
-          <t>testing-per-testing-policy</t>
+          <t>testing-per-policy, testing-per-policy</t>
         </is>
       </c>
     </row>
@@ -1353,12 +1309,12 @@
       </c>
       <c r="D3" s="15" t="inlineStr">
         <is>
-          <t>GitHub Pull Request page (Conversation tab) · 1 facts extracted · 7 people · 4 ambiguity flag(s)</t>
+          <t>GitHub Pull Request page (Conversation tab) · 32 facts extracted · 7 people · 4 ambiguity flag(s)</t>
         </is>
       </c>
       <c r="E3" s="15" t="inlineStr">
         <is>
-          <t>code-review-before-merge-to-main, code-review-before-merge-to-main, code-review-before-merge-to-main, code-review-before-merge-to-main, independent-reviewer-approval, independent-reviewer-approval, independent-reviewer-approval, independent-reviewer-approval, testing-per-testing-policy, testing-per-testing-policy</t>
+          <t>code-review-prior-to-merge, code-review-prior-to-merge, code-review-prior-to-merge, independent-reviewer-approval, independent-reviewer-approval, independent-reviewer-approval, independent-reviewer-approval, testing-per-policy</t>
         </is>
       </c>
     </row>
@@ -1378,12 +1334,12 @@
       </c>
       <c r="D4" s="15" t="inlineStr">
         <is>
-          <t>GitHub Actions workflow run summary · 1 facts extracted · 1 people · 5 ambiguity flag(s)</t>
+          <t>GitHub Actions workflow run summary page · 16 facts extracted · 1 people · 5 ambiguity flag(s)</t>
         </is>
       </c>
       <c r="E4" s="15" t="inlineStr">
         <is>
-          <t>testing-per-testing-policy, testing-per-testing-policy</t>
+          <t>testing-per-policy</t>
         </is>
       </c>
     </row>
@@ -1398,7 +1354,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1465,7 +1421,7 @@
       </c>
       <c r="B2" s="15" t="inlineStr">
         <is>
-          <t>2026-07-03T03:32:12.174534Z</t>
+          <t>2026-07-03T03:48:14.126718Z</t>
         </is>
       </c>
       <c r="C2" s="15" t="inlineStr">
@@ -1485,13 +1441,13 @@
         <v>0</v>
       </c>
       <c r="G2" s="15" t="n">
-        <v>1441</v>
+        <v>1787</v>
       </c>
       <c r="H2" s="17" t="n">
-        <v>0.2082</v>
+        <v>0.23415</v>
       </c>
       <c r="I2" s="15" t="n">
-        <v>20593</v>
+        <v>25332</v>
       </c>
     </row>
     <row r="3">
@@ -1500,7 +1456,7 @@
       </c>
       <c r="B3" s="15" t="inlineStr">
         <is>
-          <t>2026-07-03T03:32:37.674329Z</t>
+          <t>2026-07-03T03:48:39.485414Z</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -1520,13 +1476,13 @@
         <v>0</v>
       </c>
       <c r="G3" s="15" t="n">
-        <v>1903</v>
+        <v>1988</v>
       </c>
       <c r="H3" s="17" t="n">
-        <v>0.252945</v>
+        <v>0.25932</v>
       </c>
       <c r="I3" s="15" t="n">
-        <v>25488</v>
+        <v>25349</v>
       </c>
     </row>
     <row r="4">
@@ -1535,7 +1491,7 @@
       </c>
       <c r="B4" s="15" t="inlineStr">
         <is>
-          <t>2026-07-03T03:33:00.969443Z</t>
+          <t>2026-07-03T03:49:00.506620Z</t>
         </is>
       </c>
       <c r="C4" s="15" t="inlineStr">
@@ -1555,13 +1511,13 @@
         <v>0</v>
       </c>
       <c r="G4" s="15" t="n">
-        <v>1556</v>
+        <v>1515</v>
       </c>
       <c r="H4" s="17" t="n">
-        <v>0.2262</v>
+        <v>0.223125</v>
       </c>
       <c r="I4" s="15" t="n">
-        <v>23287</v>
+        <v>21014</v>
       </c>
     </row>
     <row r="5">
@@ -1570,12 +1526,12 @@
       </c>
       <c r="B5" s="15" t="inlineStr">
         <is>
-          <t>2026-07-03T03:33:40.675628Z</t>
+          <t>2026-07-03T03:49:13.305737Z</t>
         </is>
       </c>
       <c r="C5" s="15" t="inlineStr">
         <is>
-          <t>judge:code-review-before-merge-to-main:sample-1</t>
+          <t>judge:code-review-prior-to-merge:sample-1</t>
         </is>
       </c>
       <c r="D5" s="15" t="inlineStr">
@@ -1584,19 +1540,19 @@
         </is>
       </c>
       <c r="E5" s="15" t="n">
-        <v>17781</v>
+        <v>6270</v>
       </c>
       <c r="F5" s="15" t="n">
-        <v>0</v>
+        <v>3666</v>
       </c>
       <c r="G5" s="15" t="n">
-        <v>3199</v>
+        <v>1005</v>
       </c>
       <c r="H5" s="17" t="n">
-        <v>0.50664</v>
+        <v>0.119934</v>
       </c>
       <c r="I5" s="15" t="n">
-        <v>14174</v>
+        <v>12795</v>
       </c>
     </row>
     <row r="6">
@@ -1605,7 +1561,7 @@
       </c>
       <c r="B6" s="15" t="inlineStr">
         <is>
-          <t>2026-07-03T03:34:20.967393Z</t>
+          <t>2026-07-03T03:49:26.208418Z</t>
         </is>
       </c>
       <c r="C6" s="15" t="inlineStr">
@@ -1619,19 +1575,19 @@
         </is>
       </c>
       <c r="E6" s="15" t="n">
-        <v>17817</v>
+        <v>6246</v>
       </c>
       <c r="F6" s="15" t="n">
-        <v>0</v>
+        <v>3666</v>
       </c>
       <c r="G6" s="15" t="n">
-        <v>3171</v>
+        <v>1092</v>
       </c>
       <c r="H6" s="17" t="n">
-        <v>0.50508</v>
+        <v>0.126099</v>
       </c>
       <c r="I6" s="15" t="n">
-        <v>13992</v>
+        <v>12900</v>
       </c>
     </row>
     <row r="7">
@@ -1640,12 +1596,12 @@
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>2026-07-03T03:35:30.646658Z</t>
+          <t>2026-07-03T03:49:45.900071Z</t>
         </is>
       </c>
       <c r="C7" s="15" t="inlineStr">
         <is>
-          <t>judge:testing-per-testing-policy:sample-1</t>
+          <t>judge:testing-per-policy:sample-1</t>
         </is>
       </c>
       <c r="D7" s="15" t="inlineStr">
@@ -1654,19 +1610,19 @@
         </is>
       </c>
       <c r="E7" s="15" t="n">
-        <v>23199</v>
+        <v>8041</v>
       </c>
       <c r="F7" s="15" t="n">
-        <v>0</v>
+        <v>3666</v>
       </c>
       <c r="G7" s="15" t="n">
-        <v>5402</v>
+        <v>1578</v>
       </c>
       <c r="H7" s="17" t="n">
-        <v>0.753135</v>
+        <v>0.189474</v>
       </c>
       <c r="I7" s="15" t="n">
-        <v>26173</v>
+        <v>19689</v>
       </c>
     </row>
     <row r="8">
@@ -1675,7 +1631,7 @@
       </c>
       <c r="B8" s="15" t="inlineStr">
         <is>
-          <t>2026-07-03T03:35:54.379157Z</t>
+          <t>2026-07-03T03:50:10.052239Z</t>
         </is>
       </c>
       <c r="C8" s="15" t="inlineStr">
@@ -1695,39 +1651,529 @@
         <v>0</v>
       </c>
       <c r="G8" s="15" t="n">
-        <v>1605</v>
+        <v>1616</v>
       </c>
       <c r="H8" s="17" t="n">
-        <v>0.229335</v>
+        <v>0.23016</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>23722</v>
+        <v>24142</v>
       </c>
     </row>
     <row r="9">
-      <c r="C9" s="18" t="inlineStr">
+      <c r="A9" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-03T03:50:31.032351Z</t>
+        </is>
+      </c>
+      <c r="C9" s="15" t="inlineStr">
+        <is>
+          <t>screenshot:Screenshot 2025-11-14 at 14-32-05 feat use Node.js timers by default by bartlomieju · Pull Request #31272 · denoland_deno.png</t>
+        </is>
+      </c>
+      <c r="D9" s="15" t="inlineStr">
+        <is>
+          <t>claude-opus-4-7</t>
+        </is>
+      </c>
+      <c r="E9" s="15" t="n">
+        <v>7295</v>
+      </c>
+      <c r="F9" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="15" t="n">
+        <v>1504</v>
+      </c>
+      <c r="H9" s="17" t="n">
+        <v>0.222225</v>
+      </c>
+      <c r="I9" s="15" t="n">
+        <v>20969</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="15" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-03T03:50:44.382655Z</t>
+        </is>
+      </c>
+      <c r="C10" s="15" t="inlineStr">
+        <is>
+          <t>judge:code-review-prior-to-merge:sample-2</t>
+        </is>
+      </c>
+      <c r="D10" s="15" t="inlineStr">
+        <is>
+          <t>claude-opus-4-7</t>
+        </is>
+      </c>
+      <c r="E10" s="15" t="n">
+        <v>4057</v>
+      </c>
+      <c r="F10" s="15" t="n">
+        <v>3666</v>
+      </c>
+      <c r="G10" s="15" t="n">
+        <v>1067</v>
+      </c>
+      <c r="H10" s="17" t="n">
+        <v>0.091389</v>
+      </c>
+      <c r="I10" s="15" t="n">
+        <v>13346</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="15" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-03T03:50:57.753305Z</t>
+        </is>
+      </c>
+      <c r="C11" s="15" t="inlineStr">
+        <is>
+          <t>judge:independent-reviewer-approval:sample-2</t>
+        </is>
+      </c>
+      <c r="D11" s="15" t="inlineStr">
+        <is>
+          <t>claude-opus-4-7</t>
+        </is>
+      </c>
+      <c r="E11" s="15" t="n">
+        <v>4033</v>
+      </c>
+      <c r="F11" s="15" t="n">
+        <v>3666</v>
+      </c>
+      <c r="G11" s="15" t="n">
+        <v>1108</v>
+      </c>
+      <c r="H11" s="17" t="n">
+        <v>0.09410399999999999</v>
+      </c>
+      <c r="I11" s="15" t="n">
+        <v>13368</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="15" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-03T03:51:17.209066Z</t>
+        </is>
+      </c>
+      <c r="C12" s="15" t="inlineStr">
+        <is>
+          <t>judge:testing-per-policy:sample-2</t>
+        </is>
+      </c>
+      <c r="D12" s="15" t="inlineStr">
+        <is>
+          <t>claude-opus-4-7</t>
+        </is>
+      </c>
+      <c r="E12" s="15" t="n">
+        <v>5828</v>
+      </c>
+      <c r="F12" s="15" t="n">
+        <v>3666</v>
+      </c>
+      <c r="G12" s="15" t="n">
+        <v>1487</v>
+      </c>
+      <c r="H12" s="17" t="n">
+        <v>0.149454</v>
+      </c>
+      <c r="I12" s="15" t="n">
+        <v>19453</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="15" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-03T03:51:31.339364Z</t>
+        </is>
+      </c>
+      <c r="C13" s="15" t="inlineStr">
+        <is>
+          <t>screenshot:kubernetes-pr-checks.png</t>
+        </is>
+      </c>
+      <c r="D13" s="15" t="inlineStr">
+        <is>
+          <t>claude-opus-4-7</t>
+        </is>
+      </c>
+      <c r="E13" s="15" t="n">
+        <v>4703</v>
+      </c>
+      <c r="F13" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="15" t="n">
+        <v>945</v>
+      </c>
+      <c r="H13" s="17" t="n">
+        <v>0.14142</v>
+      </c>
+      <c r="I13" s="15" t="n">
+        <v>14122</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="15" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-03T03:52:34.116483Z</t>
+        </is>
+      </c>
+      <c r="C14" s="15" t="inlineStr">
+        <is>
+          <t>screenshot:kubernetes-pr.png</t>
+        </is>
+      </c>
+      <c r="D14" s="15" t="inlineStr">
+        <is>
+          <t>claude-opus-4-7</t>
+        </is>
+      </c>
+      <c r="E14" s="15" t="n">
+        <v>4172</v>
+      </c>
+      <c r="F14" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="15" t="n">
+        <v>4640</v>
+      </c>
+      <c r="H14" s="17" t="n">
+        <v>0.41058</v>
+      </c>
+      <c r="I14" s="15" t="n">
+        <v>62769</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-03T03:52:46.504782Z</t>
+        </is>
+      </c>
+      <c r="C15" s="15" t="inlineStr">
+        <is>
+          <t>judge:code-review-prior-to-merge:sample-3</t>
+        </is>
+      </c>
+      <c r="D15" s="15" t="inlineStr">
+        <is>
+          <t>claude-opus-4-7</t>
+        </is>
+      </c>
+      <c r="E15" s="15" t="n">
+        <v>6582</v>
+      </c>
+      <c r="F15" s="15" t="n">
+        <v>3666</v>
+      </c>
+      <c r="G15" s="15" t="n">
+        <v>1002</v>
+      </c>
+      <c r="H15" s="17" t="n">
+        <v>0.124389</v>
+      </c>
+      <c r="I15" s="15" t="n">
+        <v>12384</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="15" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-03T03:53:04.324724Z</t>
+        </is>
+      </c>
+      <c r="C16" s="15" t="inlineStr">
+        <is>
+          <t>judge:independent-reviewer-approval:sample-3</t>
+        </is>
+      </c>
+      <c r="D16" s="15" t="inlineStr">
+        <is>
+          <t>claude-opus-4-7</t>
+        </is>
+      </c>
+      <c r="E16" s="15" t="n">
+        <v>6558</v>
+      </c>
+      <c r="F16" s="15" t="n">
+        <v>3666</v>
+      </c>
+      <c r="G16" s="15" t="n">
+        <v>1257</v>
+      </c>
+      <c r="H16" s="17" t="n">
+        <v>0.143154</v>
+      </c>
+      <c r="I16" s="15" t="n">
+        <v>17817</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-03T03:53:22.086254Z</t>
+        </is>
+      </c>
+      <c r="C17" s="15" t="inlineStr">
+        <is>
+          <t>judge:testing-per-policy:sample-3</t>
+        </is>
+      </c>
+      <c r="D17" s="15" t="inlineStr">
+        <is>
+          <t>claude-opus-4-7</t>
+        </is>
+      </c>
+      <c r="E17" s="15" t="n">
+        <v>8353</v>
+      </c>
+      <c r="F17" s="15" t="n">
+        <v>3666</v>
+      </c>
+      <c r="G17" s="15" t="n">
+        <v>1369</v>
+      </c>
+      <c r="H17" s="17" t="n">
+        <v>0.178479</v>
+      </c>
+      <c r="I17" s="15" t="n">
+        <v>17758</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="15" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-03T03:53:36.065782Z</t>
+        </is>
+      </c>
+      <c r="C18" s="15" t="inlineStr">
+        <is>
+          <t>screenshot:nextjs-pr-checks.png</t>
+        </is>
+      </c>
+      <c r="D18" s="15" t="inlineStr">
+        <is>
+          <t>claude-opus-4-7</t>
+        </is>
+      </c>
+      <c r="E18" s="15" t="n">
+        <v>4702</v>
+      </c>
+      <c r="F18" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="15" t="n">
+        <v>924</v>
+      </c>
+      <c r="H18" s="17" t="n">
+        <v>0.13983</v>
+      </c>
+      <c r="I18" s="15" t="n">
+        <v>13972</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="15" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-03T03:54:01.769450Z</t>
+        </is>
+      </c>
+      <c r="C19" s="15" t="inlineStr">
+        <is>
+          <t>screenshot:nextjs-pr.png</t>
+        </is>
+      </c>
+      <c r="D19" s="15" t="inlineStr">
+        <is>
+          <t>claude-opus-4-7</t>
+        </is>
+      </c>
+      <c r="E19" s="15" t="n">
+        <v>6103</v>
+      </c>
+      <c r="F19" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="15" t="n">
+        <v>1808</v>
+      </c>
+      <c r="H19" s="17" t="n">
+        <v>0.227145</v>
+      </c>
+      <c r="I19" s="15" t="n">
+        <v>25696</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="15" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-03T03:54:15.073618Z</t>
+        </is>
+      </c>
+      <c r="C20" s="15" t="inlineStr">
+        <is>
+          <t>judge:code-review-prior-to-merge:sample-4</t>
+        </is>
+      </c>
+      <c r="D20" s="15" t="inlineStr">
+        <is>
+          <t>claude-opus-4-7</t>
+        </is>
+      </c>
+      <c r="E20" s="15" t="n">
+        <v>3730</v>
+      </c>
+      <c r="F20" s="15" t="n">
+        <v>3666</v>
+      </c>
+      <c r="G20" s="15" t="n">
+        <v>989</v>
+      </c>
+      <c r="H20" s="17" t="n">
+        <v>0.080634</v>
+      </c>
+      <c r="I20" s="15" t="n">
+        <v>13300</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="15" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-03T03:54:26.858373Z</t>
+        </is>
+      </c>
+      <c r="C21" s="15" t="inlineStr">
+        <is>
+          <t>judge:independent-reviewer-approval:sample-4</t>
+        </is>
+      </c>
+      <c r="D21" s="15" t="inlineStr">
+        <is>
+          <t>claude-opus-4-7</t>
+        </is>
+      </c>
+      <c r="E21" s="15" t="n">
+        <v>3706</v>
+      </c>
+      <c r="F21" s="15" t="n">
+        <v>3666</v>
+      </c>
+      <c r="G21" s="15" t="n">
+        <v>902</v>
+      </c>
+      <c r="H21" s="17" t="n">
+        <v>0.073749</v>
+      </c>
+      <c r="I21" s="15" t="n">
+        <v>11782</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="15" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-03T03:54:43.961668Z</t>
+        </is>
+      </c>
+      <c r="C22" s="15" t="inlineStr">
+        <is>
+          <t>judge:testing-per-policy:sample-4</t>
+        </is>
+      </c>
+      <c r="D22" s="15" t="inlineStr">
+        <is>
+          <t>claude-opus-4-7</t>
+        </is>
+      </c>
+      <c r="E22" s="15" t="n">
+        <v>5501</v>
+      </c>
+      <c r="F22" s="15" t="n">
+        <v>3666</v>
+      </c>
+      <c r="G22" s="15" t="n">
+        <v>1265</v>
+      </c>
+      <c r="H22" s="17" t="n">
+        <v>0.127899</v>
+      </c>
+      <c r="I22" s="15" t="n">
+        <v>17098</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="C23" s="18" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="E9" s="18">
-        <f>SUM(E2:E8)</f>
+      <c r="E23" s="18">
+        <f>SUM(E2:E22)</f>
         <v/>
       </c>
-      <c r="F9" s="18">
-        <f>SUM(F2:F8)</f>
+      <c r="F23" s="18">
+        <f>SUM(F2:F22)</f>
         <v/>
       </c>
-      <c r="G9" s="18">
-        <f>SUM(G2:G8)</f>
+      <c r="G23" s="18">
+        <f>SUM(G2:G22)</f>
         <v/>
       </c>
-      <c r="H9" s="19">
-        <f>SUM(H2:H8)</f>
+      <c r="H23" s="19">
+        <f>SUM(H2:H22)</f>
         <v/>
       </c>
-      <c r="I9" s="18">
-        <f>SUM(I2:I8)</f>
+      <c r="I23" s="18">
+        <f>SUM(I2:I22)</f>
         <v/>
       </c>
     </row>

--- a/output/independent-code-review/claude/sample-1/workpaper.xlsx
+++ b/output/independent-code-review/claude/sample-1/workpaper.xlsx
@@ -11,7 +11,6 @@
     <sheet name="Attribute Verdicts" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Evidence Citations" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Evidence Inventory" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Decision Log" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,10 +19,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.0000"/>
-  </numFmts>
-  <fonts count="12">
+  <numFmts count="0"/>
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -88,10 +85,6 @@
       <b val="1"/>
       <color rgb="000B362C"/>
       <sz val="10"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="000B362C"/>
     </font>
   </fonts>
   <fills count="4">
@@ -182,7 +175,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -208,11 +201,6 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1346,838 +1334,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I23"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="55" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="14" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B1" s="14" t="inlineStr">
-        <is>
-          <t>Timestamp</t>
-        </is>
-      </c>
-      <c r="C1" s="14" t="inlineStr">
-        <is>
-          <t>Purpose</t>
-        </is>
-      </c>
-      <c r="D1" s="14" t="inlineStr">
-        <is>
-          <t>Model</t>
-        </is>
-      </c>
-      <c r="E1" s="14" t="inlineStr">
-        <is>
-          <t>Input tokens</t>
-        </is>
-      </c>
-      <c r="F1" s="14" t="inlineStr">
-        <is>
-          <t>Cache read</t>
-        </is>
-      </c>
-      <c r="G1" s="14" t="inlineStr">
-        <is>
-          <t>Output tokens</t>
-        </is>
-      </c>
-      <c r="H1" s="14" t="inlineStr">
-        <is>
-          <t>Cost USD</t>
-        </is>
-      </c>
-      <c r="I1" s="14" t="inlineStr">
-        <is>
-          <t>Latency (ms)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" s="15" t="inlineStr">
-        <is>
-          <t>2026-07-03T03:48:14.126718Z</t>
-        </is>
-      </c>
-      <c r="C2" s="15" t="inlineStr">
-        <is>
-          <t>screenshot:Screenshot 2025-11-14 at 14-27-50 Coverage Report.png</t>
-        </is>
-      </c>
-      <c r="D2" s="15" t="inlineStr">
-        <is>
-          <t>claude-opus-4-7</t>
-        </is>
-      </c>
-      <c r="E2" s="15" t="n">
-        <v>6675</v>
-      </c>
-      <c r="F2" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" s="15" t="n">
-        <v>1787</v>
-      </c>
-      <c r="H2" s="17" t="n">
-        <v>0.23415</v>
-      </c>
-      <c r="I2" s="15" t="n">
-        <v>25332</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" s="15" t="inlineStr">
-        <is>
-          <t>2026-07-03T03:48:39.485414Z</t>
-        </is>
-      </c>
-      <c r="C3" s="15" t="inlineStr">
-        <is>
-          <t>screenshot:Screenshot 2025-11-14 at 14-28-31 Shrink relationComplexityError test size by jakebailey · Pull Request #62754 · microsoft_TypeScript.png</t>
-        </is>
-      </c>
-      <c r="D3" s="15" t="inlineStr">
-        <is>
-          <t>claude-opus-4-7</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="n">
-        <v>7348</v>
-      </c>
-      <c r="F3" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" s="15" t="n">
-        <v>1988</v>
-      </c>
-      <c r="H3" s="17" t="n">
-        <v>0.25932</v>
-      </c>
-      <c r="I3" s="15" t="n">
-        <v>25349</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" s="15" t="inlineStr">
-        <is>
-          <t>2026-07-03T03:49:00.506620Z</t>
-        </is>
-      </c>
-      <c r="C4" s="15" t="inlineStr">
-        <is>
-          <t>screenshot:Screenshot 2025-11-14 at 14-29-21 Shrink relationComplexityError test size · microsoft_TypeScript@9e76dd2.png</t>
-        </is>
-      </c>
-      <c r="D4" s="15" t="inlineStr">
-        <is>
-          <t>claude-opus-4-7</t>
-        </is>
-      </c>
-      <c r="E4" s="15" t="n">
-        <v>7300</v>
-      </c>
-      <c r="F4" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" s="15" t="n">
-        <v>1515</v>
-      </c>
-      <c r="H4" s="17" t="n">
-        <v>0.223125</v>
-      </c>
-      <c r="I4" s="15" t="n">
-        <v>21014</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" s="15" t="inlineStr">
-        <is>
-          <t>2026-07-03T03:49:13.305737Z</t>
-        </is>
-      </c>
-      <c r="C5" s="15" t="inlineStr">
-        <is>
-          <t>judge:code-review-prior-to-merge:sample-1</t>
-        </is>
-      </c>
-      <c r="D5" s="15" t="inlineStr">
-        <is>
-          <t>claude-opus-4-7</t>
-        </is>
-      </c>
-      <c r="E5" s="15" t="n">
-        <v>6270</v>
-      </c>
-      <c r="F5" s="15" t="n">
-        <v>3666</v>
-      </c>
-      <c r="G5" s="15" t="n">
-        <v>1005</v>
-      </c>
-      <c r="H5" s="17" t="n">
-        <v>0.119934</v>
-      </c>
-      <c r="I5" s="15" t="n">
-        <v>12795</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="15" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" s="15" t="inlineStr">
-        <is>
-          <t>2026-07-03T03:49:26.208418Z</t>
-        </is>
-      </c>
-      <c r="C6" s="15" t="inlineStr">
-        <is>
-          <t>judge:independent-reviewer-approval:sample-1</t>
-        </is>
-      </c>
-      <c r="D6" s="15" t="inlineStr">
-        <is>
-          <t>claude-opus-4-7</t>
-        </is>
-      </c>
-      <c r="E6" s="15" t="n">
-        <v>6246</v>
-      </c>
-      <c r="F6" s="15" t="n">
-        <v>3666</v>
-      </c>
-      <c r="G6" s="15" t="n">
-        <v>1092</v>
-      </c>
-      <c r="H6" s="17" t="n">
-        <v>0.126099</v>
-      </c>
-      <c r="I6" s="15" t="n">
-        <v>12900</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="15" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" s="15" t="inlineStr">
-        <is>
-          <t>2026-07-03T03:49:45.900071Z</t>
-        </is>
-      </c>
-      <c r="C7" s="15" t="inlineStr">
-        <is>
-          <t>judge:testing-per-policy:sample-1</t>
-        </is>
-      </c>
-      <c r="D7" s="15" t="inlineStr">
-        <is>
-          <t>claude-opus-4-7</t>
-        </is>
-      </c>
-      <c r="E7" s="15" t="n">
-        <v>8041</v>
-      </c>
-      <c r="F7" s="15" t="n">
-        <v>3666</v>
-      </c>
-      <c r="G7" s="15" t="n">
-        <v>1578</v>
-      </c>
-      <c r="H7" s="17" t="n">
-        <v>0.189474</v>
-      </c>
-      <c r="I7" s="15" t="n">
-        <v>19689</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="15" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" s="15" t="inlineStr">
-        <is>
-          <t>2026-07-03T03:50:10.052239Z</t>
-        </is>
-      </c>
-      <c r="C8" s="15" t="inlineStr">
-        <is>
-          <t>screenshot:Screenshot 2025-11-14 at 14-31-38 feat use Node.js timers by default · denoland_deno@12cde71.png</t>
-        </is>
-      </c>
-      <c r="D8" s="15" t="inlineStr">
-        <is>
-          <t>claude-opus-4-7</t>
-        </is>
-      </c>
-      <c r="E8" s="15" t="n">
-        <v>7264</v>
-      </c>
-      <c r="F8" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" s="15" t="n">
-        <v>1616</v>
-      </c>
-      <c r="H8" s="17" t="n">
-        <v>0.23016</v>
-      </c>
-      <c r="I8" s="15" t="n">
-        <v>24142</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="15" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" s="15" t="inlineStr">
-        <is>
-          <t>2026-07-03T03:50:31.032351Z</t>
-        </is>
-      </c>
-      <c r="C9" s="15" t="inlineStr">
-        <is>
-          <t>screenshot:Screenshot 2025-11-14 at 14-32-05 feat use Node.js timers by default by bartlomieju · Pull Request #31272 · denoland_deno.png</t>
-        </is>
-      </c>
-      <c r="D9" s="15" t="inlineStr">
-        <is>
-          <t>claude-opus-4-7</t>
-        </is>
-      </c>
-      <c r="E9" s="15" t="n">
-        <v>7295</v>
-      </c>
-      <c r="F9" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" s="15" t="n">
-        <v>1504</v>
-      </c>
-      <c r="H9" s="17" t="n">
-        <v>0.222225</v>
-      </c>
-      <c r="I9" s="15" t="n">
-        <v>20969</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="15" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" s="15" t="inlineStr">
-        <is>
-          <t>2026-07-03T03:50:44.382655Z</t>
-        </is>
-      </c>
-      <c r="C10" s="15" t="inlineStr">
-        <is>
-          <t>judge:code-review-prior-to-merge:sample-2</t>
-        </is>
-      </c>
-      <c r="D10" s="15" t="inlineStr">
-        <is>
-          <t>claude-opus-4-7</t>
-        </is>
-      </c>
-      <c r="E10" s="15" t="n">
-        <v>4057</v>
-      </c>
-      <c r="F10" s="15" t="n">
-        <v>3666</v>
-      </c>
-      <c r="G10" s="15" t="n">
-        <v>1067</v>
-      </c>
-      <c r="H10" s="17" t="n">
-        <v>0.091389</v>
-      </c>
-      <c r="I10" s="15" t="n">
-        <v>13346</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="15" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" s="15" t="inlineStr">
-        <is>
-          <t>2026-07-03T03:50:57.753305Z</t>
-        </is>
-      </c>
-      <c r="C11" s="15" t="inlineStr">
-        <is>
-          <t>judge:independent-reviewer-approval:sample-2</t>
-        </is>
-      </c>
-      <c r="D11" s="15" t="inlineStr">
-        <is>
-          <t>claude-opus-4-7</t>
-        </is>
-      </c>
-      <c r="E11" s="15" t="n">
-        <v>4033</v>
-      </c>
-      <c r="F11" s="15" t="n">
-        <v>3666</v>
-      </c>
-      <c r="G11" s="15" t="n">
-        <v>1108</v>
-      </c>
-      <c r="H11" s="17" t="n">
-        <v>0.09410399999999999</v>
-      </c>
-      <c r="I11" s="15" t="n">
-        <v>13368</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="15" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" s="15" t="inlineStr">
-        <is>
-          <t>2026-07-03T03:51:17.209066Z</t>
-        </is>
-      </c>
-      <c r="C12" s="15" t="inlineStr">
-        <is>
-          <t>judge:testing-per-policy:sample-2</t>
-        </is>
-      </c>
-      <c r="D12" s="15" t="inlineStr">
-        <is>
-          <t>claude-opus-4-7</t>
-        </is>
-      </c>
-      <c r="E12" s="15" t="n">
-        <v>5828</v>
-      </c>
-      <c r="F12" s="15" t="n">
-        <v>3666</v>
-      </c>
-      <c r="G12" s="15" t="n">
-        <v>1487</v>
-      </c>
-      <c r="H12" s="17" t="n">
-        <v>0.149454</v>
-      </c>
-      <c r="I12" s="15" t="n">
-        <v>19453</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="15" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" s="15" t="inlineStr">
-        <is>
-          <t>2026-07-03T03:51:31.339364Z</t>
-        </is>
-      </c>
-      <c r="C13" s="15" t="inlineStr">
-        <is>
-          <t>screenshot:kubernetes-pr-checks.png</t>
-        </is>
-      </c>
-      <c r="D13" s="15" t="inlineStr">
-        <is>
-          <t>claude-opus-4-7</t>
-        </is>
-      </c>
-      <c r="E13" s="15" t="n">
-        <v>4703</v>
-      </c>
-      <c r="F13" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" s="15" t="n">
-        <v>945</v>
-      </c>
-      <c r="H13" s="17" t="n">
-        <v>0.14142</v>
-      </c>
-      <c r="I13" s="15" t="n">
-        <v>14122</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="15" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" s="15" t="inlineStr">
-        <is>
-          <t>2026-07-03T03:52:34.116483Z</t>
-        </is>
-      </c>
-      <c r="C14" s="15" t="inlineStr">
-        <is>
-          <t>screenshot:kubernetes-pr.png</t>
-        </is>
-      </c>
-      <c r="D14" s="15" t="inlineStr">
-        <is>
-          <t>claude-opus-4-7</t>
-        </is>
-      </c>
-      <c r="E14" s="15" t="n">
-        <v>4172</v>
-      </c>
-      <c r="F14" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" s="15" t="n">
-        <v>4640</v>
-      </c>
-      <c r="H14" s="17" t="n">
-        <v>0.41058</v>
-      </c>
-      <c r="I14" s="15" t="n">
-        <v>62769</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="15" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" s="15" t="inlineStr">
-        <is>
-          <t>2026-07-03T03:52:46.504782Z</t>
-        </is>
-      </c>
-      <c r="C15" s="15" t="inlineStr">
-        <is>
-          <t>judge:code-review-prior-to-merge:sample-3</t>
-        </is>
-      </c>
-      <c r="D15" s="15" t="inlineStr">
-        <is>
-          <t>claude-opus-4-7</t>
-        </is>
-      </c>
-      <c r="E15" s="15" t="n">
-        <v>6582</v>
-      </c>
-      <c r="F15" s="15" t="n">
-        <v>3666</v>
-      </c>
-      <c r="G15" s="15" t="n">
-        <v>1002</v>
-      </c>
-      <c r="H15" s="17" t="n">
-        <v>0.124389</v>
-      </c>
-      <c r="I15" s="15" t="n">
-        <v>12384</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="15" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" s="15" t="inlineStr">
-        <is>
-          <t>2026-07-03T03:53:04.324724Z</t>
-        </is>
-      </c>
-      <c r="C16" s="15" t="inlineStr">
-        <is>
-          <t>judge:independent-reviewer-approval:sample-3</t>
-        </is>
-      </c>
-      <c r="D16" s="15" t="inlineStr">
-        <is>
-          <t>claude-opus-4-7</t>
-        </is>
-      </c>
-      <c r="E16" s="15" t="n">
-        <v>6558</v>
-      </c>
-      <c r="F16" s="15" t="n">
-        <v>3666</v>
-      </c>
-      <c r="G16" s="15" t="n">
-        <v>1257</v>
-      </c>
-      <c r="H16" s="17" t="n">
-        <v>0.143154</v>
-      </c>
-      <c r="I16" s="15" t="n">
-        <v>17817</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="15" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" s="15" t="inlineStr">
-        <is>
-          <t>2026-07-03T03:53:22.086254Z</t>
-        </is>
-      </c>
-      <c r="C17" s="15" t="inlineStr">
-        <is>
-          <t>judge:testing-per-policy:sample-3</t>
-        </is>
-      </c>
-      <c r="D17" s="15" t="inlineStr">
-        <is>
-          <t>claude-opus-4-7</t>
-        </is>
-      </c>
-      <c r="E17" s="15" t="n">
-        <v>8353</v>
-      </c>
-      <c r="F17" s="15" t="n">
-        <v>3666</v>
-      </c>
-      <c r="G17" s="15" t="n">
-        <v>1369</v>
-      </c>
-      <c r="H17" s="17" t="n">
-        <v>0.178479</v>
-      </c>
-      <c r="I17" s="15" t="n">
-        <v>17758</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="15" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" s="15" t="inlineStr">
-        <is>
-          <t>2026-07-03T03:53:36.065782Z</t>
-        </is>
-      </c>
-      <c r="C18" s="15" t="inlineStr">
-        <is>
-          <t>screenshot:nextjs-pr-checks.png</t>
-        </is>
-      </c>
-      <c r="D18" s="15" t="inlineStr">
-        <is>
-          <t>claude-opus-4-7</t>
-        </is>
-      </c>
-      <c r="E18" s="15" t="n">
-        <v>4702</v>
-      </c>
-      <c r="F18" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" s="15" t="n">
-        <v>924</v>
-      </c>
-      <c r="H18" s="17" t="n">
-        <v>0.13983</v>
-      </c>
-      <c r="I18" s="15" t="n">
-        <v>13972</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="15" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" s="15" t="inlineStr">
-        <is>
-          <t>2026-07-03T03:54:01.769450Z</t>
-        </is>
-      </c>
-      <c r="C19" s="15" t="inlineStr">
-        <is>
-          <t>screenshot:nextjs-pr.png</t>
-        </is>
-      </c>
-      <c r="D19" s="15" t="inlineStr">
-        <is>
-          <t>claude-opus-4-7</t>
-        </is>
-      </c>
-      <c r="E19" s="15" t="n">
-        <v>6103</v>
-      </c>
-      <c r="F19" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" s="15" t="n">
-        <v>1808</v>
-      </c>
-      <c r="H19" s="17" t="n">
-        <v>0.227145</v>
-      </c>
-      <c r="I19" s="15" t="n">
-        <v>25696</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="15" t="n">
-        <v>19</v>
-      </c>
-      <c r="B20" s="15" t="inlineStr">
-        <is>
-          <t>2026-07-03T03:54:15.073618Z</t>
-        </is>
-      </c>
-      <c r="C20" s="15" t="inlineStr">
-        <is>
-          <t>judge:code-review-prior-to-merge:sample-4</t>
-        </is>
-      </c>
-      <c r="D20" s="15" t="inlineStr">
-        <is>
-          <t>claude-opus-4-7</t>
-        </is>
-      </c>
-      <c r="E20" s="15" t="n">
-        <v>3730</v>
-      </c>
-      <c r="F20" s="15" t="n">
-        <v>3666</v>
-      </c>
-      <c r="G20" s="15" t="n">
-        <v>989</v>
-      </c>
-      <c r="H20" s="17" t="n">
-        <v>0.080634</v>
-      </c>
-      <c r="I20" s="15" t="n">
-        <v>13300</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="15" t="n">
-        <v>20</v>
-      </c>
-      <c r="B21" s="15" t="inlineStr">
-        <is>
-          <t>2026-07-03T03:54:26.858373Z</t>
-        </is>
-      </c>
-      <c r="C21" s="15" t="inlineStr">
-        <is>
-          <t>judge:independent-reviewer-approval:sample-4</t>
-        </is>
-      </c>
-      <c r="D21" s="15" t="inlineStr">
-        <is>
-          <t>claude-opus-4-7</t>
-        </is>
-      </c>
-      <c r="E21" s="15" t="n">
-        <v>3706</v>
-      </c>
-      <c r="F21" s="15" t="n">
-        <v>3666</v>
-      </c>
-      <c r="G21" s="15" t="n">
-        <v>902</v>
-      </c>
-      <c r="H21" s="17" t="n">
-        <v>0.073749</v>
-      </c>
-      <c r="I21" s="15" t="n">
-        <v>11782</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="15" t="n">
-        <v>21</v>
-      </c>
-      <c r="B22" s="15" t="inlineStr">
-        <is>
-          <t>2026-07-03T03:54:43.961668Z</t>
-        </is>
-      </c>
-      <c r="C22" s="15" t="inlineStr">
-        <is>
-          <t>judge:testing-per-policy:sample-4</t>
-        </is>
-      </c>
-      <c r="D22" s="15" t="inlineStr">
-        <is>
-          <t>claude-opus-4-7</t>
-        </is>
-      </c>
-      <c r="E22" s="15" t="n">
-        <v>5501</v>
-      </c>
-      <c r="F22" s="15" t="n">
-        <v>3666</v>
-      </c>
-      <c r="G22" s="15" t="n">
-        <v>1265</v>
-      </c>
-      <c r="H22" s="17" t="n">
-        <v>0.127899</v>
-      </c>
-      <c r="I22" s="15" t="n">
-        <v>17098</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="C23" s="18" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="E23" s="18">
-        <f>SUM(E2:E22)</f>
-        <v/>
-      </c>
-      <c r="F23" s="18">
-        <f>SUM(F2:F22)</f>
-        <v/>
-      </c>
-      <c r="G23" s="18">
-        <f>SUM(G2:G22)</f>
-        <v/>
-      </c>
-      <c r="H23" s="19">
-        <f>SUM(H2:H22)</f>
-        <v/>
-      </c>
-      <c r="I23" s="18">
-        <f>SUM(I2:I22)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/output/independent-code-review/claude/sample-1/workpaper.xlsx
+++ b/output/independent-code-review/claude/sample-1/workpaper.xlsx
@@ -11,6 +11,7 @@
     <sheet name="Attribute Verdicts" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Evidence Citations" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Evidence Inventory" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Decision Log" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,8 +20,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="11">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.0000"/>
+  </numFmts>
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -85,6 +88,10 @@
       <b val="1"/>
       <color rgb="000B362C"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="000B362C"/>
     </font>
   </fonts>
   <fills count="4">
@@ -175,7 +182,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -201,6 +208,11 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -621,7 +633,7 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>claude:claude-opus-4-7</t>
+          <t>claude:claude-opus-4-8</t>
         </is>
       </c>
     </row>
@@ -633,7 +645,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>03 Jul 2026, 03:49 UTC</t>
+          <t>03 Jul 2026, 04:17 UTC</t>
         </is>
       </c>
     </row>
@@ -855,7 +867,7 @@
       </c>
       <c r="D2" s="15" t="inlineStr">
         <is>
-          <t>A pull request (#62754) exists for the change and shows a human approval from RyanCavanaugh recorded at "17 hours ago", while the merge to microsoft:main occurred "16 hours ago" — i.e. the approval preceded the merge. The PR page shows the change was merged via the PR (merge commit ea48ded into microsoft:main), not committed directly to main, satisfying the 4-eyes / no-direct-commit criterion for this attribute. Independence of the reviewer is a separate attribute and is not judged here.</t>
+          <t>A pull request review record exists for PR #62754: RyanCavanaugh (a different human from author/committer jakebailey) approved the changes. The approval event appears in the timeline at "17 hours ago" while the merge into microsoft:main occurred at "16 hours ago", so approval preceded the merge. Auto-merge (squash) was enabled and the branch only merged after the approval and checks completed, consistent with review being required prior to committing to main.</t>
         </is>
       </c>
       <c r="E2" s="15" t="n">
@@ -863,7 +875,7 @@
       </c>
       <c r="F2" s="15" t="inlineStr">
         <is>
-          <t>Copilot AI review — not counted toward this attribute since the human approval by RyanCavanaugh already satisfies the 'code review completed before merge' criterion; independence of reviewer is judged under a separate attribute.</t>
+          <t>Copilot AI review is present but was not relied upon — an AI reviewer is not an independent human; the independent human approval came from RyanCavanaugh, which satisfies this attribute (approval-timing/existence). Reviewer-independence nuances belong to a separate attribute.</t>
         </is>
       </c>
     </row>
@@ -883,15 +895,16 @@
       </c>
       <c r="D3" s="15" t="inlineStr">
         <is>
-          <t>The PR was authored and merged by jakebailey, and the approving reviewer is RyanCavanaugh — a different named human — whose approval (green check) is recorded in the timeline prior to the merge event. Copilot's review is not counted as an independent human approval, but RyanCavanaugh's approval satisfies the 4-eyes requirement on its own. No evidence indicates RyanCavanaugh committed or co-authored the change (single commit 9e76dd2 attributed to jakebailey).</t>
+          <t>The change author/committer/merger is jakebailey, and the approving review ("RyanCavanaugh approved these changes") was given by RyanCavanaugh — a different named human — satisfying the 4-eyes principle. RyanCavanaugh has no authorship or committer role on the PR (author, assignee, and merger are all jakebailey). The other listed "reviewer", Copilot, is an AI and is correctly disregarded as a non-independent human reviewer; the independent human approval from RyanCavanaugh still stands.</t>
         </is>
       </c>
       <c r="E3" s="15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F3" s="15" t="inlineStr">
         <is>
-          <t>Copilot AI review — rejected as an independent reviewer because it is not a human; however RyanCavanaugh provides an independent human approval, so the criterion is still met.</t>
+          <t>Copilot as reviewer — rejected as an independent reviewer because it is an AI, not a human; independence is instead established by RyanCavanaugh's human approval.
+Author self-approval — not applicable; the approval came from RyanCavanaugh, not the author jakebailey.</t>
         </is>
       </c>
     </row>
@@ -907,20 +920,19 @@
         </is>
       </c>
       <c r="C4" s="15" t="n">
-        <v>0.78</v>
+        <v>0.83</v>
       </c>
       <c r="D4" s="15" t="inlineStr">
         <is>
-          <t>The change is a test-size reduction (+10/-10 in a test file, "Shrink relationComplexityError test size"), which is a behavior-preserving refactor of test code — an exception category under the policy, but even without invoking it the coverage report shows Statements 94.62%, Branches 89.48%, Functions 94.79% (all above the 80%/70%/80% thresholds). CI ran the full test matrix (15 jobs across Node 14–24, coverage, lint, knip, format, browser-integration, typecheck, smoke, baselines) with status Success and 36 of 37 checks passed, and results are visible as PR status checks. A coverage report artifact (39.2 MB) was generated by the coverage job and a coverage dashboard screenshot was captured as part of the review. No line-coverage percentage is directly shown (only Bytes/Statements/Branches/Functions) but Statements is the standard proxy and comfortably exceeds 80%.</t>
+          <t>This PR is test-only maintenance: all 4 changed files are under tests/cases/ and tests/baselines/, and the description ("Shrink relationComplexityError test size... Getting tired of this test timing out on slower builders") confirms no production code is touched. The testing policy's exception for refactoring/test-only maintenance applies, so the coverage thresholds do not gate this specific change. Independent of the exception, CI ran and passed the 15-job matrix (Status: Success, 17m 44s) with a coverage artifact generated, so tests demonstrably ran in the pipeline before merge. The standalone coverage report screenshot cannot be tied to this PR (no repo/branch/commit visible), but that is not needed given the exception.</t>
         </is>
       </c>
       <c r="E4" s="15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F4" s="15" t="inlineStr">
         <is>
-          <t>Refactoring with No Behavioral Changes: the PR shrinks the size of an existing test (relationComplexityError) to avoid timeouts on slower builders — behavior-preserving test refactor. Accepted as applicable, though not required because measured coverage already exceeds thresholds.
-Line coverage column is not shown in the coverage report (only Bytes/Statements/Branches/Functions). Statements coverage 94.62% is treated as the practical equivalent for the 80% line-coverage criterion; noted as a minor ambiguity but not fatal given the large margin above threshold.</t>
+          <t>Refactoring with No Behavioral Changes / test-only maintenance — ACCEPTED: all 4 touched files are under tests/cases/ and tests/baselines/, the change only reduces the size of an existing compiler test (Digits literals 10→8, combinations 10,000→4,096), and no production/application code is modified. Coverage thresholds therefore do not gate this change.</t>
         </is>
       </c>
     </row>
@@ -935,7 +947,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -979,12 +991,12 @@
       </c>
       <c r="C2" s="15" t="inlineStr">
         <is>
-          <t>PR header and Merged status badge</t>
+          <t>Timeline — 'RyanCavanaugh approved these changes 17 hours ago' (green check, 'View reviewed changes' link)</t>
         </is>
       </c>
       <c r="D2" s="15" t="inlineStr">
         <is>
-          <t>PR #62754 exists in microsoft/TypeScript with status 'Merged'; header states 'jakebailey merged 1 commit into microsoft:main from jakebailey:relationComplexityErrorSmaller 16 hours ago'.</t>
+          <t>A human reviewer, RyanCavanaugh, approved the PR; this is the code review record and its approval event.</t>
         </is>
       </c>
     </row>
@@ -1001,12 +1013,12 @@
       </c>
       <c r="C3" s="15" t="inlineStr">
         <is>
-          <t>Timeline — approval event</t>
+          <t>PR header line + merge event</t>
         </is>
       </c>
       <c r="D3" s="15" t="inlineStr">
         <is>
-          <t>'RyanCavanaugh approved these changes 17 hours ago' with a green check, and Reviewers sidebar shows RyanCavanaugh with a green check.</t>
+          <t>Header shows jakebailey merged into microsoft:main '16 hours ago' and merge event 'jakebailey merged commit ea48ded into microsoft:main 16 hours ago' — later than the '17 hours ago' approval, so approval preceded merge.</t>
         </is>
       </c>
     </row>
@@ -1023,12 +1035,12 @@
       </c>
       <c r="C4" s="15" t="inlineStr">
         <is>
-          <t>Merge event line</t>
+          <t>Timeline — 'jakebailey enabled auto-merge (squash) 17 hours ago' and Reviewers side panel</t>
         </is>
       </c>
       <c r="D4" s="15" t="inlineStr">
         <is>
-          <t>'jakebailey merged commit ea48ded into microsoft:main 16 hours ago' — merge occurred one hour after the approval, i.e. after approval was recorded.</t>
+          <t>Auto-merge was enabled and RyanCavanaugh shows a green approval checkmark; the branch merged only after approval, indicating the review gated the merge to main.</t>
         </is>
       </c>
     </row>
@@ -1045,12 +1057,12 @@
       </c>
       <c r="C5" s="15" t="inlineStr">
         <is>
-          <t>PR header</t>
+          <t>Timeline event with green check</t>
         </is>
       </c>
       <c r="D5" s="15" t="inlineStr">
         <is>
-          <t>'jakebailey merged 1 commit into microsoft:main from jakebailey:relationComplexityErrorSmaller' — identifies jakebailey as both author and merger.</t>
+          <t>'RyanCavanaugh approved these changes 17 hours ago' — an independent human approval, distinct from the author.</t>
         </is>
       </c>
     </row>
@@ -1067,12 +1079,12 @@
       </c>
       <c r="C6" s="15" t="inlineStr">
         <is>
-          <t>Timeline — approval event</t>
+          <t>PR header / Assignees side panel</t>
         </is>
       </c>
       <c r="D6" s="15" t="inlineStr">
         <is>
-          <t>'RyanCavanaugh approved these changes 17 hours ago' with green check, occurring before the merge event 16 hours ago.</t>
+          <t>jakebailey is the author, committer, assignee, and the person who merged the PR; RyanCavanaugh is not in any author/committer role.</t>
         </is>
       </c>
     </row>
@@ -1089,19 +1101,19 @@
       </c>
       <c r="C7" s="15" t="inlineStr">
         <is>
-          <t>Reviewers sidebar</t>
+          <t>Reviewers side panel</t>
         </is>
       </c>
       <c r="D7" s="15" t="inlineStr">
         <is>
-          <t>RyanCavanaugh listed with green check (✓); Copilot listed without a check — Copilot is a bot, not an independent human reviewer.</t>
+          <t>Reviewers list shows Copilot (AI, not independent human) and RyanCavanaugh (green checkmark, human approver).</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="15" t="inlineStr">
         <is>
-          <t>Code Review approvals are performed by independent code reviewers</t>
+          <t>Testing is performed in accordance with the testing policy</t>
         </is>
       </c>
       <c r="B8" s="15" t="inlineStr">
@@ -1111,12 +1123,12 @@
       </c>
       <c r="C8" s="15" t="inlineStr">
         <is>
-          <t>Commit reference in timeline</t>
+          <t>Reviewed Changes table (Files changed = 4) and opening comment</t>
         </is>
       </c>
       <c r="D8" s="15" t="inlineStr">
         <is>
-          <t>Single commit 9e76dd2 for 'Shrink_relationComplexityError_test_size' is associated with the PR (authored by jakebailey per branch context); no indication RyanCavanaugh co-authored or committed.</t>
+          <t>All 4 changed files are under tests/cases/compiler/ and tests/baselines/reference/; diff is +10 -10; author comment says the change shrinks a test that was timing out on slower builders — test-only maintenance, no production code.</t>
         </is>
       </c>
     </row>
@@ -1128,17 +1140,17 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>Screenshot 2025-11-14 at 14-27-50 Coverage Report.png</t>
+          <t>Screenshot 2025-11-14 at 14-29-21 Shrink relationComplexityError test size · microsoft_TypeScript@9e76dd2.png</t>
         </is>
       </c>
       <c r="C9" s="15" t="inlineStr">
         <is>
-          <t>Summary row (top of table)</t>
+          <t>Workflow run status/duration header and Jobs sidebar</t>
         </is>
       </c>
       <c r="D9" s="15" t="inlineStr">
         <is>
-          <t>Statements 94.62%, Branches 89.48%, Functions 94.79% — all above policy thresholds of 80/70/80.</t>
+          <t>CI workflow run for this PR shows Status: Success, total duration 17m 44s, 15 matrix jobs completed with green checks, plus coverage/lint/smoke/baselines jobs — tests ran in the pipeline before merge.</t>
         </is>
       </c>
     </row>
@@ -1150,61 +1162,17 @@
       </c>
       <c r="B10" s="15" t="inlineStr">
         <is>
-          <t>Screenshot 2025-11-14 at 14-29-21 Shrink relationComplexityError test size · microsoft_TypeScript@9e76dd2.png</t>
+          <t>Screenshot 2025-11-14 at 14-27-50 Coverage Report.png</t>
         </is>
       </c>
       <c r="C10" s="15" t="inlineStr">
         <is>
-          <t>Workflow run header and Jobs sidebar</t>
+          <t>Summary row and ambiguities note</t>
         </is>
       </c>
       <c r="D10" s="15" t="inlineStr">
         <is>
-          <t>CI run #34653 status Success, 17m 44s, 15 matrix jobs plus coverage/lint/knip/format/browser-integration/typecheck/smoke/baselines all green; coverage artifact 39.2 MB produced.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="15" t="inlineStr">
-        <is>
-          <t>Testing is performed in accordance with the testing policy</t>
-        </is>
-      </c>
-      <c r="B11" s="15" t="inlineStr">
-        <is>
-          <t>Screenshot 2025-11-14 at 14-28-31 Shrink relationComplexityError test size by jakebailey · Pull Request #62754 · microsoft_TypeScript.png</t>
-        </is>
-      </c>
-      <c r="C11" s="15" t="inlineStr">
-        <is>
-          <t>Merge status bar / checks summary</t>
-        </is>
-      </c>
-      <c r="D11" s="15" t="inlineStr">
-        <is>
-          <t>'36 of 37 checks passed' shown on the merged PR; PR title 'Shrink relationComplexityError test size', +10/-10 across 4 files — a test-shrinking refactor.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="15" t="inlineStr">
-        <is>
-          <t>Testing is performed in accordance with the testing policy</t>
-        </is>
-      </c>
-      <c r="B12" s="15" t="inlineStr">
-        <is>
-          <t>Screenshot 2025-11-14 at 14-27-50 Coverage Report.png</t>
-        </is>
-      </c>
-      <c r="C12" s="15" t="inlineStr">
-        <is>
-          <t>Page header</t>
-        </is>
-      </c>
-      <c r="D12" s="15" t="inlineStr">
-        <is>
-          <t>'Coverage Report' dashboard was generated and captured, evidencing that a coverage report exists for review.</t>
+          <t>A coverage report exists (Statements 94.62%, Branches 89.48%, Functions 94.79%) but shows no repo/branch/commit/build ID, so it cannot be tied to this specific PR; not required here because the test-only exception applies.</t>
         </is>
       </c>
     </row>
@@ -1272,12 +1240,12 @@
       </c>
       <c r="D2" s="15" t="inlineStr">
         <is>
-          <t>Coverage report dashboard · 1 facts extracted · 6 ambiguity flag(s)</t>
+          <t>Coverage Report dashboard (interactive coverage table, likely Istanbul/nyc-style or similar HTML coverage viewer) · 13 facts extracted · 7 ambiguity flag(s)</t>
         </is>
       </c>
       <c r="E2" s="15" t="inlineStr">
         <is>
-          <t>testing-per-policy, testing-per-policy</t>
+          <t>testing-per-testing-policy</t>
         </is>
       </c>
     </row>
@@ -1297,12 +1265,12 @@
       </c>
       <c r="D3" s="15" t="inlineStr">
         <is>
-          <t>GitHub Pull Request page (Conversation tab) · 32 facts extracted · 7 people · 4 ambiguity flag(s)</t>
+          <t>GitHub Pull Request page (Conversation tab) · 33 facts extracted · 8 people · 5 ambiguity flag(s)</t>
         </is>
       </c>
       <c r="E3" s="15" t="inlineStr">
         <is>
-          <t>code-review-prior-to-merge, code-review-prior-to-merge, code-review-prior-to-merge, independent-reviewer-approval, independent-reviewer-approval, independent-reviewer-approval, independent-reviewer-approval, testing-per-policy</t>
+          <t>code-review-before-commit-to-main, code-review-before-commit-to-main, code-review-before-commit-to-main, independent-reviewer-approval, independent-reviewer-approval, independent-reviewer-approval, testing-per-testing-policy</t>
         </is>
       </c>
     </row>
@@ -1322,13 +1290,847 @@
       </c>
       <c r="D4" s="15" t="inlineStr">
         <is>
-          <t>GitHub Actions workflow run summary page · 16 facts extracted · 1 people · 5 ambiguity flag(s)</t>
+          <t>GitHub Actions workflow run summary page · 18 facts extracted · 1 people · 6 ambiguity flag(s)</t>
         </is>
       </c>
       <c r="E4" s="15" t="inlineStr">
         <is>
-          <t>testing-per-policy</t>
-        </is>
+          <t>testing-per-testing-policy</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="55" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="14" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B1" s="14" t="inlineStr">
+        <is>
+          <t>Timestamp</t>
+        </is>
+      </c>
+      <c r="C1" s="14" t="inlineStr">
+        <is>
+          <t>Purpose</t>
+        </is>
+      </c>
+      <c r="D1" s="14" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="E1" s="14" t="inlineStr">
+        <is>
+          <t>Input tokens</t>
+        </is>
+      </c>
+      <c r="F1" s="14" t="inlineStr">
+        <is>
+          <t>Cache read</t>
+        </is>
+      </c>
+      <c r="G1" s="14" t="inlineStr">
+        <is>
+          <t>Output tokens</t>
+        </is>
+      </c>
+      <c r="H1" s="14" t="inlineStr">
+        <is>
+          <t>Cost USD</t>
+        </is>
+      </c>
+      <c r="I1" s="14" t="inlineStr">
+        <is>
+          <t>Latency (ms)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-03T04:15:40.084130Z</t>
+        </is>
+      </c>
+      <c r="C2" s="15" t="inlineStr">
+        <is>
+          <t>screenshot:Screenshot 2025-11-14 at 14-27-50 Coverage Report.png</t>
+        </is>
+      </c>
+      <c r="D2" s="15" t="inlineStr">
+        <is>
+          <t>claude-opus-4-8</t>
+        </is>
+      </c>
+      <c r="E2" s="15" t="n">
+        <v>4474</v>
+      </c>
+      <c r="F2" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" s="15" t="n">
+        <v>1660</v>
+      </c>
+      <c r="H2" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" s="15" t="n">
+        <v>23603</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-03T04:16:06.122392Z</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>screenshot:Screenshot 2025-11-14 at 14-28-31 Shrink relationComplexityError test size by jakebailey · Pull Request #62754 · microsoft_TypeScript.png</t>
+        </is>
+      </c>
+      <c r="D3" s="15" t="inlineStr">
+        <is>
+          <t>claude-opus-4-8</t>
+        </is>
+      </c>
+      <c r="E3" s="15" t="n">
+        <v>5147</v>
+      </c>
+      <c r="F3" s="15" t="n">
+        <v>1802</v>
+      </c>
+      <c r="G3" s="15" t="n">
+        <v>2338</v>
+      </c>
+      <c r="H3" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" s="15" t="n">
+        <v>26026</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-03T04:16:30.394765Z</t>
+        </is>
+      </c>
+      <c r="C4" s="15" t="inlineStr">
+        <is>
+          <t>screenshot:Screenshot 2025-11-14 at 14-29-21 Shrink relationComplexityError test size · microsoft_TypeScript@9e76dd2.png</t>
+        </is>
+      </c>
+      <c r="D4" s="15" t="inlineStr">
+        <is>
+          <t>claude-opus-4-8</t>
+        </is>
+      </c>
+      <c r="E4" s="15" t="n">
+        <v>5099</v>
+      </c>
+      <c r="F4" s="15" t="n">
+        <v>1802</v>
+      </c>
+      <c r="G4" s="15" t="n">
+        <v>1763</v>
+      </c>
+      <c r="H4" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="15" t="n">
+        <v>24264</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-03T04:16:44.295721Z</t>
+        </is>
+      </c>
+      <c r="C5" s="15" t="inlineStr">
+        <is>
+          <t>judge:code-review-before-commit-to-main:sample-1</t>
+        </is>
+      </c>
+      <c r="D5" s="15" t="inlineStr">
+        <is>
+          <t>claude-opus-4-8</t>
+        </is>
+      </c>
+      <c r="E5" s="15" t="n">
+        <v>6383</v>
+      </c>
+      <c r="F5" s="15" t="n">
+        <v>5151</v>
+      </c>
+      <c r="G5" s="15" t="n">
+        <v>1065</v>
+      </c>
+      <c r="H5" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="15" t="n">
+        <v>13897</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-03T04:16:55.782597Z</t>
+        </is>
+      </c>
+      <c r="C6" s="15" t="inlineStr">
+        <is>
+          <t>judge:independent-reviewer-approval:sample-1</t>
+        </is>
+      </c>
+      <c r="D6" s="15" t="inlineStr">
+        <is>
+          <t>claude-opus-4-8</t>
+        </is>
+      </c>
+      <c r="E6" s="15" t="n">
+        <v>6355</v>
+      </c>
+      <c r="F6" s="15" t="n">
+        <v>5151</v>
+      </c>
+      <c r="G6" s="15" t="n">
+        <v>927</v>
+      </c>
+      <c r="H6" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="15" t="n">
+        <v>11484</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="15" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-03T04:17:11.438826Z</t>
+        </is>
+      </c>
+      <c r="C7" s="15" t="inlineStr">
+        <is>
+          <t>judge:testing-per-testing-policy:sample-1</t>
+        </is>
+      </c>
+      <c r="D7" s="15" t="inlineStr">
+        <is>
+          <t>claude-opus-4-8</t>
+        </is>
+      </c>
+      <c r="E7" s="15" t="n">
+        <v>8116</v>
+      </c>
+      <c r="F7" s="15" t="n">
+        <v>5151</v>
+      </c>
+      <c r="G7" s="15" t="n">
+        <v>1317</v>
+      </c>
+      <c r="H7" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="15" t="n">
+        <v>15655</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="15" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-03T04:17:34.006071Z</t>
+        </is>
+      </c>
+      <c r="C8" s="15" t="inlineStr">
+        <is>
+          <t>screenshot:Screenshot 2025-11-14 at 14-31-38 feat use Node.js timers by default · denoland_deno@12cde71.png</t>
+        </is>
+      </c>
+      <c r="D8" s="15" t="inlineStr">
+        <is>
+          <t>claude-opus-4-8</t>
+        </is>
+      </c>
+      <c r="E8" s="15" t="n">
+        <v>5063</v>
+      </c>
+      <c r="F8" s="15" t="n">
+        <v>1802</v>
+      </c>
+      <c r="G8" s="15" t="n">
+        <v>1746</v>
+      </c>
+      <c r="H8" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="15" t="n">
+        <v>22559</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-03T04:17:57.834234Z</t>
+        </is>
+      </c>
+      <c r="C9" s="15" t="inlineStr">
+        <is>
+          <t>screenshot:Screenshot 2025-11-14 at 14-32-05 feat use Node.js timers by default by bartlomieju · Pull Request #31272 · denoland_deno.png</t>
+        </is>
+      </c>
+      <c r="D9" s="15" t="inlineStr">
+        <is>
+          <t>claude-opus-4-8</t>
+        </is>
+      </c>
+      <c r="E9" s="15" t="n">
+        <v>5094</v>
+      </c>
+      <c r="F9" s="15" t="n">
+        <v>1802</v>
+      </c>
+      <c r="G9" s="15" t="n">
+        <v>1921</v>
+      </c>
+      <c r="H9" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="15" t="n">
+        <v>23819</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="15" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-03T04:18:09.107798Z</t>
+        </is>
+      </c>
+      <c r="C10" s="15" t="inlineStr">
+        <is>
+          <t>judge:code-review-before-commit-to-main:sample-2</t>
+        </is>
+      </c>
+      <c r="D10" s="15" t="inlineStr">
+        <is>
+          <t>claude-opus-4-8</t>
+        </is>
+      </c>
+      <c r="E10" s="15" t="n">
+        <v>4233</v>
+      </c>
+      <c r="F10" s="15" t="n">
+        <v>5151</v>
+      </c>
+      <c r="G10" s="15" t="n">
+        <v>946</v>
+      </c>
+      <c r="H10" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="15" t="n">
+        <v>11269</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="15" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-03T04:18:20.213919Z</t>
+        </is>
+      </c>
+      <c r="C11" s="15" t="inlineStr">
+        <is>
+          <t>judge:independent-reviewer-approval:sample-2</t>
+        </is>
+      </c>
+      <c r="D11" s="15" t="inlineStr">
+        <is>
+          <t>claude-opus-4-8</t>
+        </is>
+      </c>
+      <c r="E11" s="15" t="n">
+        <v>4205</v>
+      </c>
+      <c r="F11" s="15" t="n">
+        <v>5151</v>
+      </c>
+      <c r="G11" s="15" t="n">
+        <v>943</v>
+      </c>
+      <c r="H11" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="15" t="n">
+        <v>11102</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="15" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-03T04:18:39.404920Z</t>
+        </is>
+      </c>
+      <c r="C12" s="15" t="inlineStr">
+        <is>
+          <t>judge:testing-per-testing-policy:sample-2</t>
+        </is>
+      </c>
+      <c r="D12" s="15" t="inlineStr">
+        <is>
+          <t>claude-opus-4-8</t>
+        </is>
+      </c>
+      <c r="E12" s="15" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F12" s="15" t="n">
+        <v>5151</v>
+      </c>
+      <c r="G12" s="15" t="n">
+        <v>1616</v>
+      </c>
+      <c r="H12" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="15" t="n">
+        <v>19186</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="15" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-03T04:18:52.612761Z</t>
+        </is>
+      </c>
+      <c r="C13" s="15" t="inlineStr">
+        <is>
+          <t>screenshot:kubernetes-pr-checks.png</t>
+        </is>
+      </c>
+      <c r="D13" s="15" t="inlineStr">
+        <is>
+          <t>claude-opus-4-8</t>
+        </is>
+      </c>
+      <c r="E13" s="15" t="n">
+        <v>2502</v>
+      </c>
+      <c r="F13" s="15" t="n">
+        <v>1802</v>
+      </c>
+      <c r="G13" s="15" t="n">
+        <v>963</v>
+      </c>
+      <c r="H13" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="15" t="n">
+        <v>13198</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="15" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-03T04:19:22.610986Z</t>
+        </is>
+      </c>
+      <c r="C14" s="15" t="inlineStr">
+        <is>
+          <t>screenshot:kubernetes-pr.png</t>
+        </is>
+      </c>
+      <c r="D14" s="15" t="inlineStr">
+        <is>
+          <t>claude-opus-4-8</t>
+        </is>
+      </c>
+      <c r="E14" s="15" t="n">
+        <v>1971</v>
+      </c>
+      <c r="F14" s="15" t="n">
+        <v>1802</v>
+      </c>
+      <c r="G14" s="15" t="n">
+        <v>2247</v>
+      </c>
+      <c r="H14" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="15" t="n">
+        <v>29989</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-03T04:19:35.659572Z</t>
+        </is>
+      </c>
+      <c r="C15" s="15" t="inlineStr">
+        <is>
+          <t>judge:code-review-before-commit-to-main:sample-3</t>
+        </is>
+      </c>
+      <c r="D15" s="15" t="inlineStr">
+        <is>
+          <t>claude-opus-4-8</t>
+        </is>
+      </c>
+      <c r="E15" s="15" t="n">
+        <v>3818</v>
+      </c>
+      <c r="F15" s="15" t="n">
+        <v>5151</v>
+      </c>
+      <c r="G15" s="15" t="n">
+        <v>1030</v>
+      </c>
+      <c r="H15" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" s="15" t="n">
+        <v>13044</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="15" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-03T04:19:48.832139Z</t>
+        </is>
+      </c>
+      <c r="C16" s="15" t="inlineStr">
+        <is>
+          <t>judge:independent-reviewer-approval:sample-3</t>
+        </is>
+      </c>
+      <c r="D16" s="15" t="inlineStr">
+        <is>
+          <t>claude-opus-4-8</t>
+        </is>
+      </c>
+      <c r="E16" s="15" t="n">
+        <v>3790</v>
+      </c>
+      <c r="F16" s="15" t="n">
+        <v>5151</v>
+      </c>
+      <c r="G16" s="15" t="n">
+        <v>994</v>
+      </c>
+      <c r="H16" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" s="15" t="n">
+        <v>13169</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-03T04:20:03.784191Z</t>
+        </is>
+      </c>
+      <c r="C17" s="15" t="inlineStr">
+        <is>
+          <t>judge:testing-per-testing-policy:sample-3</t>
+        </is>
+      </c>
+      <c r="D17" s="15" t="inlineStr">
+        <is>
+          <t>claude-opus-4-8</t>
+        </is>
+      </c>
+      <c r="E17" s="15" t="n">
+        <v>5551</v>
+      </c>
+      <c r="F17" s="15" t="n">
+        <v>5151</v>
+      </c>
+      <c r="G17" s="15" t="n">
+        <v>1256</v>
+      </c>
+      <c r="H17" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" s="15" t="n">
+        <v>14948</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="15" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-03T04:20:18.239343Z</t>
+        </is>
+      </c>
+      <c r="C18" s="15" t="inlineStr">
+        <is>
+          <t>screenshot:nextjs-pr-checks.png</t>
+        </is>
+      </c>
+      <c r="D18" s="15" t="inlineStr">
+        <is>
+          <t>claude-opus-4-8</t>
+        </is>
+      </c>
+      <c r="E18" s="15" t="n">
+        <v>2501</v>
+      </c>
+      <c r="F18" s="15" t="n">
+        <v>1802</v>
+      </c>
+      <c r="G18" s="15" t="n">
+        <v>1103</v>
+      </c>
+      <c r="H18" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" s="15" t="n">
+        <v>14446</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="15" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-03T04:20:41.669803Z</t>
+        </is>
+      </c>
+      <c r="C19" s="15" t="inlineStr">
+        <is>
+          <t>screenshot:nextjs-pr.png</t>
+        </is>
+      </c>
+      <c r="D19" s="15" t="inlineStr">
+        <is>
+          <t>claude-opus-4-8</t>
+        </is>
+      </c>
+      <c r="E19" s="15" t="n">
+        <v>3902</v>
+      </c>
+      <c r="F19" s="15" t="n">
+        <v>1802</v>
+      </c>
+      <c r="G19" s="15" t="n">
+        <v>1798</v>
+      </c>
+      <c r="H19" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="15" t="n">
+        <v>23426</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="15" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-03T04:20:53.838524Z</t>
+        </is>
+      </c>
+      <c r="C20" s="15" t="inlineStr">
+        <is>
+          <t>judge:code-review-before-commit-to-main:sample-4</t>
+        </is>
+      </c>
+      <c r="D20" s="15" t="inlineStr">
+        <is>
+          <t>claude-opus-4-8</t>
+        </is>
+      </c>
+      <c r="E20" s="15" t="n">
+        <v>3513</v>
+      </c>
+      <c r="F20" s="15" t="n">
+        <v>5151</v>
+      </c>
+      <c r="G20" s="15" t="n">
+        <v>912</v>
+      </c>
+      <c r="H20" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="15" t="n">
+        <v>12165</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="15" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-03T04:21:02.663985Z</t>
+        </is>
+      </c>
+      <c r="C21" s="15" t="inlineStr">
+        <is>
+          <t>judge:independent-reviewer-approval:sample-4</t>
+        </is>
+      </c>
+      <c r="D21" s="15" t="inlineStr">
+        <is>
+          <t>claude-opus-4-8</t>
+        </is>
+      </c>
+      <c r="E21" s="15" t="n">
+        <v>3485</v>
+      </c>
+      <c r="F21" s="15" t="n">
+        <v>5151</v>
+      </c>
+      <c r="G21" s="15" t="n">
+        <v>711</v>
+      </c>
+      <c r="H21" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" s="15" t="n">
+        <v>8821</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="15" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-03T04:21:19.635538Z</t>
+        </is>
+      </c>
+      <c r="C22" s="15" t="inlineStr">
+        <is>
+          <t>judge:testing-per-testing-policy:sample-4</t>
+        </is>
+      </c>
+      <c r="D22" s="15" t="inlineStr">
+        <is>
+          <t>claude-opus-4-8</t>
+        </is>
+      </c>
+      <c r="E22" s="15" t="n">
+        <v>5246</v>
+      </c>
+      <c r="F22" s="15" t="n">
+        <v>5151</v>
+      </c>
+      <c r="G22" s="15" t="n">
+        <v>1284</v>
+      </c>
+      <c r="H22" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" s="15" t="n">
+        <v>16967</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="C23" s="18" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="E23" s="18">
+        <f>SUM(E2:E22)</f>
+        <v/>
+      </c>
+      <c r="F23" s="18">
+        <f>SUM(F2:F22)</f>
+        <v/>
+      </c>
+      <c r="G23" s="18">
+        <f>SUM(G2:G22)</f>
+        <v/>
+      </c>
+      <c r="H23" s="19">
+        <f>SUM(H2:H22)</f>
+        <v/>
+      </c>
+      <c r="I23" s="18">
+        <f>SUM(I2:I22)</f>
+        <v/>
       </c>
     </row>
   </sheetData>
